--- a/encode_pairs.xlsx
+++ b/encode_pairs.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IBEB\Documents\GitHub\SEED\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vera/Documents/GitHub/SEED/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38493091-46BD-A546-8F3F-39247EB7B4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="1120" windowWidth="24640" windowHeight="16880"/>
+    <workbookView xWindow="1160" yWindow="1120" windowWidth="24640" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="262">
   <si>
     <t>Index</t>
   </si>
@@ -809,8 +811,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -830,11 +832,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -846,25 +850,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -910,6 +920,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -918,10 +936,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -1201,30 +1219,33 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z91"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="36.10938" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16.10938" style="3" customWidth="1"/>
-    <col min="4" max="4" width="16.66406" style="2" customWidth="1"/>
-    <col min="5" max="5" width="40.10938" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.44141" style="2" customWidth="1"/>
+    <col min="1" max="1" width="7.1640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="36.1640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="40.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.5" style="2" customWidth="1"/>
     <col min="7" max="7" width="15" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.66406" style="2" customWidth="1"/>
-    <col min="9" max="9" width="39.44141" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.33203" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14.66406" style="2" customWidth="1"/>
-    <col min="12" max="12" width="15.66406" style="2" customWidth="1"/>
-    <col min="13" max="13" width="16.44141" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="10.77734" style="2"/>
+    <col min="8" max="8" width="17.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="39.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="16.5" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15.75">
+    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1280,7 +1301,7 @@
       <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -1336,7 +1357,7 @@
       <c r="Y2" s="7"/>
       <c r="Z2" s="7"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -1392,7 +1413,7 @@
       <c r="Y3" s="7"/>
       <c r="Z3" s="7"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -1433,7 +1454,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>2.1000000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
@@ -1448,7 +1469,7 @@
       <c r="Y4" s="7"/>
       <c r="Z4" s="7"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -1489,7 +1510,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>2.1499999999999999</v>
+        <v>2.15</v>
       </c>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
@@ -1504,7 +1525,7 @@
       <c r="Y5" s="7"/>
       <c r="Z5" s="7"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -1560,7 +1581,7 @@
       <c r="Y6" s="7"/>
       <c r="Z6" s="7"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>6</v>
       </c>
@@ -1616,7 +1637,7 @@
       <c r="Y7" s="7"/>
       <c r="Z7" s="7"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>7</v>
       </c>
@@ -1672,7 +1693,7 @@
       <c r="Y8" s="7"/>
       <c r="Z8" s="7"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>8</v>
       </c>
@@ -1713,7 +1734,7 @@
         <v>25</v>
       </c>
       <c r="N9">
-        <v>2.3500000000000001</v>
+        <v>2.35</v>
       </c>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
@@ -1728,7 +1749,7 @@
       <c r="Y9" s="7"/>
       <c r="Z9" s="7"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>9</v>
       </c>
@@ -1769,7 +1790,7 @@
         <v>25</v>
       </c>
       <c r="N10">
-        <v>2.3999999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
@@ -1784,7 +1805,7 @@
       <c r="Y10" s="7"/>
       <c r="Z10" s="7"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>10</v>
       </c>
@@ -1840,7 +1861,7 @@
       <c r="Y11" s="7"/>
       <c r="Z11" s="7"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>11</v>
       </c>
@@ -1896,7 +1917,7 @@
       <c r="Y12" s="7"/>
       <c r="Z12" s="7"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>12</v>
       </c>
@@ -1952,7 +1973,7 @@
       <c r="Y13" s="7"/>
       <c r="Z13" s="7"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>13</v>
       </c>
@@ -1993,7 +2014,7 @@
         <v>25</v>
       </c>
       <c r="N14">
-        <v>2.6000000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
@@ -2008,7 +2029,7 @@
       <c r="Y14" s="7"/>
       <c r="Z14" s="7"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>14</v>
       </c>
@@ -2049,7 +2070,7 @@
         <v>25</v>
       </c>
       <c r="N15">
-        <v>2.6499999999999999</v>
+        <v>2.65</v>
       </c>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
@@ -2064,7 +2085,7 @@
       <c r="Y15" s="7"/>
       <c r="Z15" s="7"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>15</v>
       </c>
@@ -2105,7 +2126,7 @@
         <v>25</v>
       </c>
       <c r="N16">
-        <v>2.7000000000000002</v>
+        <v>2.7</v>
       </c>
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
@@ -2120,7 +2141,7 @@
       <c r="Y16" s="7"/>
       <c r="Z16" s="7"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>16</v>
       </c>
@@ -2176,7 +2197,7 @@
       <c r="Y17" s="7"/>
       <c r="Z17" s="7"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>17</v>
       </c>
@@ -2217,7 +2238,7 @@
         <v>25</v>
       </c>
       <c r="N18">
-        <v>2.7999999999999998</v>
+        <v>2.8</v>
       </c>
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
@@ -2232,7 +2253,7 @@
       <c r="Y18" s="7"/>
       <c r="Z18" s="7"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>18</v>
       </c>
@@ -2273,7 +2294,7 @@
         <v>25</v>
       </c>
       <c r="N19">
-        <v>2.8500000000000001</v>
+        <v>2.85</v>
       </c>
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
@@ -2288,7 +2309,7 @@
       <c r="Y19" s="7"/>
       <c r="Z19" s="7"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>19</v>
       </c>
@@ -2329,7 +2350,7 @@
         <v>25</v>
       </c>
       <c r="N20">
-        <v>2.8999999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="O20" s="7"/>
       <c r="P20" s="7"/>
@@ -2344,7 +2365,7 @@
       <c r="Y20" s="7"/>
       <c r="Z20" s="7"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>20</v>
       </c>
@@ -2385,7 +2406,7 @@
         <v>25</v>
       </c>
       <c r="N21">
-        <v>2.9500000000000002</v>
+        <v>2.95</v>
       </c>
       <c r="O21" s="7"/>
       <c r="P21" s="7"/>
@@ -2400,7 +2421,7 @@
       <c r="Y21" s="7"/>
       <c r="Z21" s="7"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>21</v>
       </c>
@@ -2456,7 +2477,7 @@
       <c r="Y22" s="7"/>
       <c r="Z22" s="7"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>22</v>
       </c>
@@ -2497,7 +2518,7 @@
         <v>25</v>
       </c>
       <c r="N23">
-        <v>3.0499999999999998</v>
+        <v>3.05</v>
       </c>
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
@@ -2512,7 +2533,7 @@
       <c r="Y23" s="7"/>
       <c r="Z23" s="7"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>23</v>
       </c>
@@ -2553,7 +2574,7 @@
         <v>25</v>
       </c>
       <c r="N24">
-        <v>3.1000000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="O24" s="7"/>
       <c r="P24" s="7"/>
@@ -2568,7 +2589,7 @@
       <c r="Y24" s="7"/>
       <c r="Z24" s="7"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>24</v>
       </c>
@@ -2609,7 +2630,7 @@
         <v>25</v>
       </c>
       <c r="N25">
-        <v>3.1499999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="O25" s="7"/>
       <c r="P25" s="7"/>
@@ -2624,7 +2645,7 @@
       <c r="Y25" s="7"/>
       <c r="Z25" s="7"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
         <v>25</v>
       </c>
@@ -2665,7 +2686,7 @@
         <v>25</v>
       </c>
       <c r="N26">
-        <v>3.2000000000000002</v>
+        <v>3.2</v>
       </c>
       <c r="O26" s="7"/>
       <c r="P26" s="7"/>
@@ -2680,7 +2701,7 @@
       <c r="Y26" s="7"/>
       <c r="Z26" s="7"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27" s="7">
         <v>26</v>
       </c>
@@ -2736,7 +2757,7 @@
       <c r="Y27" s="7"/>
       <c r="Z27" s="7"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
         <v>27</v>
       </c>
@@ -2792,7 +2813,7 @@
       <c r="Y28" s="7"/>
       <c r="Z28" s="7"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29" s="7">
         <v>28</v>
       </c>
@@ -2848,7 +2869,7 @@
       <c r="Y29" s="7"/>
       <c r="Z29" s="7"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A30" s="7">
         <v>29</v>
       </c>
@@ -2889,7 +2910,7 @@
         <v>25</v>
       </c>
       <c r="N30">
-        <v>2.1000000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="O30" s="7"/>
       <c r="P30" s="7"/>
@@ -2904,7 +2925,7 @@
       <c r="Y30" s="7"/>
       <c r="Z30" s="7"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A31" s="7">
         <v>30</v>
       </c>
@@ -2945,7 +2966,7 @@
         <v>25</v>
       </c>
       <c r="N31">
-        <v>2.1499999999999999</v>
+        <v>2.15</v>
       </c>
       <c r="O31" s="7"/>
       <c r="P31" s="7"/>
@@ -2960,7 +2981,7 @@
       <c r="Y31" s="7"/>
       <c r="Z31" s="7"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
         <v>31</v>
       </c>
@@ -3016,7 +3037,7 @@
       <c r="Y32" s="7"/>
       <c r="Z32" s="7"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A33" s="7">
         <v>32</v>
       </c>
@@ -3072,7 +3093,7 @@
       <c r="Y33" s="7"/>
       <c r="Z33" s="7"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
         <v>33</v>
       </c>
@@ -3128,7 +3149,7 @@
       <c r="Y34" s="7"/>
       <c r="Z34" s="7"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A35" s="7">
         <v>34</v>
       </c>
@@ -3169,7 +3190,7 @@
         <v>154</v>
       </c>
       <c r="N35">
-        <v>2.3500000000000001</v>
+        <v>2.35</v>
       </c>
       <c r="O35" s="7"/>
       <c r="P35" s="7"/>
@@ -3184,7 +3205,7 @@
       <c r="Y35" s="7"/>
       <c r="Z35" s="7"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
         <v>35</v>
       </c>
@@ -3225,7 +3246,7 @@
         <v>154</v>
       </c>
       <c r="N36">
-        <v>2.3999999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="O36" s="7"/>
       <c r="P36" s="7"/>
@@ -3240,7 +3261,7 @@
       <c r="Y36" s="7"/>
       <c r="Z36" s="7"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A37" s="7">
         <v>36</v>
       </c>
@@ -3296,7 +3317,7 @@
       <c r="Y37" s="7"/>
       <c r="Z37" s="7"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
         <v>37</v>
       </c>
@@ -3352,7 +3373,7 @@
       <c r="Y38" s="7"/>
       <c r="Z38" s="7"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A39" s="7">
         <v>38</v>
       </c>
@@ -3408,7 +3429,7 @@
       <c r="Y39" s="7"/>
       <c r="Z39" s="7"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A40" s="7">
         <v>39</v>
       </c>
@@ -3449,7 +3470,7 @@
         <v>154</v>
       </c>
       <c r="N40">
-        <v>2.6000000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="O40" s="7"/>
       <c r="P40" s="7"/>
@@ -3464,7 +3485,7 @@
       <c r="Y40" s="7"/>
       <c r="Z40" s="7"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A41" s="7">
         <v>40</v>
       </c>
@@ -3505,7 +3526,7 @@
         <v>154</v>
       </c>
       <c r="N41">
-        <v>2.6499999999999999</v>
+        <v>2.65</v>
       </c>
       <c r="O41" s="7"/>
       <c r="P41" s="7"/>
@@ -3520,7 +3541,7 @@
       <c r="Y41" s="7"/>
       <c r="Z41" s="7"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
         <v>41</v>
       </c>
@@ -3561,7 +3582,7 @@
         <v>154</v>
       </c>
       <c r="N42">
-        <v>2.7000000000000002</v>
+        <v>2.7</v>
       </c>
       <c r="O42" s="7"/>
       <c r="P42" s="7"/>
@@ -3576,7 +3597,7 @@
       <c r="Y42" s="7"/>
       <c r="Z42" s="7"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A43" s="7">
         <v>42</v>
       </c>
@@ -3632,7 +3653,7 @@
       <c r="Y43" s="7"/>
       <c r="Z43" s="7"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A44" s="7">
         <v>43</v>
       </c>
@@ -3673,7 +3694,7 @@
         <v>154</v>
       </c>
       <c r="N44">
-        <v>2.7999999999999998</v>
+        <v>2.8</v>
       </c>
       <c r="O44" s="7"/>
       <c r="P44" s="7"/>
@@ -3688,7 +3709,7 @@
       <c r="Y44" s="7"/>
       <c r="Z44" s="7"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A45" s="7">
         <v>44</v>
       </c>
@@ -3729,7 +3750,7 @@
         <v>154</v>
       </c>
       <c r="N45">
-        <v>2.8500000000000001</v>
+        <v>2.85</v>
       </c>
       <c r="O45" s="7"/>
       <c r="P45" s="7"/>
@@ -3744,7 +3765,7 @@
       <c r="Y45" s="7"/>
       <c r="Z45" s="7"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A46" s="7">
         <v>45</v>
       </c>
@@ -3785,7 +3806,7 @@
         <v>154</v>
       </c>
       <c r="N46">
-        <v>2.8999999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="O46" s="7"/>
       <c r="P46" s="7"/>
@@ -3800,7 +3821,7 @@
       <c r="Y46" s="7"/>
       <c r="Z46" s="7"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A47" s="7">
         <v>46</v>
       </c>
@@ -3841,7 +3862,7 @@
         <v>154</v>
       </c>
       <c r="N47">
-        <v>2.9500000000000002</v>
+        <v>2.95</v>
       </c>
       <c r="O47" s="7"/>
       <c r="P47" s="7"/>
@@ -3856,7 +3877,7 @@
       <c r="Y47" s="7"/>
       <c r="Z47" s="7"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A48" s="7">
         <v>47</v>
       </c>
@@ -3912,7 +3933,7 @@
       <c r="Y48" s="7"/>
       <c r="Z48" s="7"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A49" s="7">
         <v>48</v>
       </c>
@@ -3953,7 +3974,7 @@
         <v>154</v>
       </c>
       <c r="N49">
-        <v>3.0499999999999998</v>
+        <v>3.05</v>
       </c>
       <c r="O49" s="7"/>
       <c r="P49" s="7"/>
@@ -3968,7 +3989,7 @@
       <c r="Y49" s="7"/>
       <c r="Z49" s="7"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A50" s="7">
         <v>49</v>
       </c>
@@ -4009,7 +4030,7 @@
         <v>154</v>
       </c>
       <c r="N50">
-        <v>3.1000000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="O50" s="7"/>
       <c r="P50" s="7"/>
@@ -4024,7 +4045,7 @@
       <c r="Y50" s="7"/>
       <c r="Z50" s="7"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A51" s="7">
         <v>50</v>
       </c>
@@ -4065,7 +4086,7 @@
         <v>154</v>
       </c>
       <c r="N51">
-        <v>3.1499999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="O51" s="7"/>
       <c r="P51" s="7"/>
@@ -4080,7 +4101,7 @@
       <c r="Y51" s="7"/>
       <c r="Z51" s="7"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A52" s="7">
         <v>51</v>
       </c>
@@ -4121,7 +4142,7 @@
         <v>154</v>
       </c>
       <c r="N52">
-        <v>3.2000000000000002</v>
+        <v>3.2</v>
       </c>
       <c r="O52" s="7"/>
       <c r="P52" s="7"/>
@@ -4136,7 +4157,7 @@
       <c r="Y52" s="7"/>
       <c r="Z52" s="7"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A53" s="7">
         <v>52</v>
       </c>
@@ -4192,7 +4213,7 @@
       <c r="Y53" s="7"/>
       <c r="Z53" s="7"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A54" s="7">
         <v>53</v>
       </c>
@@ -4248,7 +4269,7 @@
       <c r="Y54" s="7"/>
       <c r="Z54" s="7"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A55" s="7">
         <v>54</v>
       </c>
@@ -4304,7 +4325,7 @@
       <c r="Y55" s="7"/>
       <c r="Z55" s="7"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A56" s="7">
         <v>55</v>
       </c>
@@ -4345,7 +4366,7 @@
         <v>154</v>
       </c>
       <c r="N56">
-        <v>2.1000000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="O56" s="7"/>
       <c r="P56" s="7"/>
@@ -4360,7 +4381,7 @@
       <c r="Y56" s="7"/>
       <c r="Z56" s="7"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A57" s="7">
         <v>56</v>
       </c>
@@ -4401,7 +4422,7 @@
         <v>154</v>
       </c>
       <c r="N57">
-        <v>2.1499999999999999</v>
+        <v>2.15</v>
       </c>
       <c r="O57" s="7"/>
       <c r="P57" s="7"/>
@@ -4416,7 +4437,7 @@
       <c r="Y57" s="7"/>
       <c r="Z57" s="7"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A58" s="7">
         <v>57</v>
       </c>
@@ -4472,7 +4493,7 @@
       <c r="Y58" s="7"/>
       <c r="Z58" s="7"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A59" s="7">
         <v>58</v>
       </c>
@@ -4528,7 +4549,7 @@
       <c r="Y59" s="7"/>
       <c r="Z59" s="7"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A60" s="7">
         <v>59</v>
       </c>
@@ -4584,7 +4605,7 @@
       <c r="Y60" s="7"/>
       <c r="Z60" s="7"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A61" s="7">
         <v>60</v>
       </c>
@@ -4625,7 +4646,7 @@
         <v>154</v>
       </c>
       <c r="N61">
-        <v>2.3500000000000001</v>
+        <v>2.35</v>
       </c>
       <c r="O61" s="7"/>
       <c r="P61" s="7"/>
@@ -4640,7 +4661,7 @@
       <c r="Y61" s="7"/>
       <c r="Z61" s="7"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A62" s="7">
         <v>61</v>
       </c>
@@ -4667,7 +4688,7 @@
       <c r="L62" s="7"/>
       <c r="M62" s="7"/>
       <c r="N62">
-        <v>2.1499999999999999</v>
+        <v>2.15</v>
       </c>
       <c r="O62" s="7"/>
       <c r="P62" s="7"/>
@@ -4682,7 +4703,7 @@
       <c r="Y62" s="7"/>
       <c r="Z62" s="7"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A63" s="7">
         <v>62</v>
       </c>
@@ -4724,7 +4745,7 @@
       <c r="Y63" s="7"/>
       <c r="Z63" s="7"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A64" s="7">
         <v>63</v>
       </c>
@@ -4766,7 +4787,7 @@
       <c r="Y64" s="7"/>
       <c r="Z64" s="7"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A65" s="7">
         <v>64</v>
       </c>
@@ -4808,7 +4829,7 @@
       <c r="Y65" s="7"/>
       <c r="Z65" s="7"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A66" s="7">
         <v>65</v>
       </c>
@@ -4835,7 +4856,7 @@
       <c r="L66" s="7"/>
       <c r="M66" s="7"/>
       <c r="N66">
-        <v>2.3500000000000001</v>
+        <v>2.35</v>
       </c>
       <c r="O66" s="7"/>
       <c r="P66" s="7"/>
@@ -4850,7 +4871,7 @@
       <c r="Y66" s="7"/>
       <c r="Z66" s="7"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A67" s="7">
         <v>66</v>
       </c>
@@ -4877,7 +4898,7 @@
       <c r="L67" s="7"/>
       <c r="M67" s="7"/>
       <c r="N67">
-        <v>2.3999999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="O67" s="7"/>
       <c r="P67" s="7"/>
@@ -4892,7 +4913,7 @@
       <c r="Y67" s="7"/>
       <c r="Z67" s="7"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A68" s="7">
         <v>67</v>
       </c>
@@ -4934,7 +4955,7 @@
       <c r="Y68" s="7"/>
       <c r="Z68" s="7"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A69" s="7">
         <v>68</v>
       </c>
@@ -4976,7 +4997,7 @@
       <c r="Y69" s="7"/>
       <c r="Z69" s="7"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A70" s="7">
         <v>69</v>
       </c>
@@ -5018,7 +5039,7 @@
       <c r="Y70" s="7"/>
       <c r="Z70" s="7"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A71" s="7">
         <v>70</v>
       </c>
@@ -5045,7 +5066,7 @@
       <c r="L71" s="7"/>
       <c r="M71" s="7"/>
       <c r="N71">
-        <v>2.6000000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="O71" s="7"/>
       <c r="P71" s="7"/>
@@ -5060,7 +5081,7 @@
       <c r="Y71" s="7"/>
       <c r="Z71" s="7"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A72" s="7">
         <v>71</v>
       </c>
@@ -5087,7 +5108,7 @@
       <c r="L72" s="7"/>
       <c r="M72" s="7"/>
       <c r="N72">
-        <v>2.6499999999999999</v>
+        <v>2.65</v>
       </c>
       <c r="O72" s="7"/>
       <c r="P72" s="7"/>
@@ -5102,7 +5123,7 @@
       <c r="Y72" s="7"/>
       <c r="Z72" s="7"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A73" s="7">
         <v>72</v>
       </c>
@@ -5129,7 +5150,7 @@
       <c r="L73" s="7"/>
       <c r="M73" s="7"/>
       <c r="N73">
-        <v>2.7000000000000002</v>
+        <v>2.7</v>
       </c>
       <c r="O73" s="7"/>
       <c r="P73" s="7"/>
@@ -5144,7 +5165,7 @@
       <c r="Y73" s="7"/>
       <c r="Z73" s="7"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A74" s="7">
         <v>73</v>
       </c>
@@ -5186,7 +5207,7 @@
       <c r="Y74" s="7"/>
       <c r="Z74" s="7"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A75" s="7">
         <v>74</v>
       </c>
@@ -5213,7 +5234,7 @@
       <c r="L75" s="7"/>
       <c r="M75" s="7"/>
       <c r="N75">
-        <v>2.7999999999999998</v>
+        <v>2.8</v>
       </c>
       <c r="O75" s="7"/>
       <c r="P75" s="7"/>
@@ -5228,7 +5249,7 @@
       <c r="Y75" s="7"/>
       <c r="Z75" s="7"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A76" s="7">
         <v>75</v>
       </c>
@@ -5255,7 +5276,7 @@
       <c r="L76" s="7"/>
       <c r="M76" s="7"/>
       <c r="N76">
-        <v>2.8500000000000001</v>
+        <v>2.85</v>
       </c>
       <c r="O76" s="7"/>
       <c r="P76" s="7"/>
@@ -5270,7 +5291,7 @@
       <c r="Y76" s="7"/>
       <c r="Z76" s="7"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A77" s="7">
         <v>76</v>
       </c>
@@ -5297,7 +5318,7 @@
       <c r="L77" s="7"/>
       <c r="M77" s="7"/>
       <c r="N77">
-        <v>2.8999999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="O77" s="7"/>
       <c r="P77" s="7"/>
@@ -5312,7 +5333,7 @@
       <c r="Y77" s="7"/>
       <c r="Z77" s="7"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A78" s="7">
         <v>77</v>
       </c>
@@ -5339,7 +5360,7 @@
       <c r="L78" s="7"/>
       <c r="M78" s="7"/>
       <c r="N78">
-        <v>2.9500000000000002</v>
+        <v>2.95</v>
       </c>
       <c r="O78" s="7"/>
       <c r="P78" s="7"/>
@@ -5354,7 +5375,7 @@
       <c r="Y78" s="7"/>
       <c r="Z78" s="7"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A79" s="7">
         <v>78</v>
       </c>
@@ -5396,7 +5417,7 @@
       <c r="Y79" s="7"/>
       <c r="Z79" s="7"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A80" s="7">
         <v>79</v>
       </c>
@@ -5423,7 +5444,7 @@
       <c r="L80" s="7"/>
       <c r="M80" s="7"/>
       <c r="N80">
-        <v>3.0499999999999998</v>
+        <v>3.05</v>
       </c>
       <c r="O80" s="7"/>
       <c r="P80" s="7"/>
@@ -5438,7 +5459,7 @@
       <c r="Y80" s="7"/>
       <c r="Z80" s="7"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A81" s="7">
         <v>80</v>
       </c>
@@ -5465,7 +5486,7 @@
       <c r="L81" s="7"/>
       <c r="M81" s="7"/>
       <c r="N81">
-        <v>3.1000000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="O81" s="7"/>
       <c r="P81" s="7"/>
@@ -5480,7 +5501,7 @@
       <c r="Y81" s="7"/>
       <c r="Z81" s="7"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A82" s="7">
         <v>81</v>
       </c>
@@ -5507,7 +5528,7 @@
       <c r="L82" s="7"/>
       <c r="M82" s="7"/>
       <c r="N82">
-        <v>3.1499999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="O82" s="7"/>
       <c r="P82" s="7"/>
@@ -5522,7 +5543,7 @@
       <c r="Y82" s="7"/>
       <c r="Z82" s="7"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A83" s="7">
         <v>82</v>
       </c>
@@ -5549,7 +5570,7 @@
       <c r="L83" s="7"/>
       <c r="M83" s="7"/>
       <c r="N83">
-        <v>3.2000000000000002</v>
+        <v>3.2</v>
       </c>
       <c r="O83" s="7"/>
       <c r="P83" s="7"/>
@@ -5564,7 +5585,7 @@
       <c r="Y83" s="7"/>
       <c r="Z83" s="7"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A84" s="7">
         <v>83</v>
       </c>
@@ -5606,7 +5627,7 @@
       <c r="Y84" s="7"/>
       <c r="Z84" s="7"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A85" s="7">
         <v>84</v>
       </c>
@@ -5648,7 +5669,7 @@
       <c r="Y85" s="7"/>
       <c r="Z85" s="7"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A86" s="7">
         <v>85</v>
       </c>
@@ -5690,7 +5711,7 @@
       <c r="Y86" s="7"/>
       <c r="Z86" s="7"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A87" s="7">
         <v>86</v>
       </c>
@@ -5717,7 +5738,7 @@
       <c r="L87" s="7"/>
       <c r="M87" s="7"/>
       <c r="N87">
-        <v>2.1000000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="O87" s="7"/>
       <c r="P87" s="7"/>
@@ -5732,7 +5753,7 @@
       <c r="Y87" s="7"/>
       <c r="Z87" s="7"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A88" s="7">
         <v>87</v>
       </c>
@@ -5759,7 +5780,7 @@
       <c r="L88" s="7"/>
       <c r="M88" s="7"/>
       <c r="N88">
-        <v>2.1499999999999999</v>
+        <v>2.15</v>
       </c>
       <c r="O88" s="7"/>
       <c r="P88" s="7"/>
@@ -5774,7 +5795,7 @@
       <c r="Y88" s="7"/>
       <c r="Z88" s="7"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A89" s="7">
         <v>88</v>
       </c>
@@ -5816,7 +5837,7 @@
       <c r="Y89" s="7"/>
       <c r="Z89" s="7"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A90" s="7">
         <v>89</v>
       </c>
@@ -5858,7 +5879,7 @@
       <c r="Y90" s="7"/>
       <c r="Z90" s="7"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A91" s="7">
         <v>90</v>
       </c>
@@ -5901,6 +5922,7 @@
       <c r="Z91" s="7"/>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="C2" numberStoredAsText="1"/>
   </ignoredErrors>

--- a/encode_pairs.xlsx
+++ b/encode_pairs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vera/Documents/GitHub/SEED/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38493091-46BD-A546-8F3F-39247EB7B4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F3C87D-885F-0446-9738-4053E48AAB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="1120" windowWidth="24640" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7560" yWindow="1120" windowWidth="24640" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="267">
   <si>
     <t>Index</t>
   </si>
@@ -721,27 +721,6 @@
     <t>Scenes_Dataset/field_B.jpg</t>
   </si>
   <si>
-    <t>Scenes_Dataset/underwater_A.jpg</t>
-  </si>
-  <si>
-    <t>Scenes_Dataset/cemetery_A.jpg</t>
-  </si>
-  <si>
-    <t>(600,452)</t>
-  </si>
-  <si>
-    <t>Scenes_Dataset/terrace_A.jpg</t>
-  </si>
-  <si>
-    <t>(600,451)</t>
-  </si>
-  <si>
-    <t>Scenes_Dataset/gymnasium_A.jpg</t>
-  </si>
-  <si>
-    <t>Scenes_Dataset/laboratory_A.jpg</t>
-  </si>
-  <si>
     <t>Scenes_Dataset/trash_A.jpg</t>
   </si>
   <si>
@@ -806,6 +785,42 @@
   </si>
   <si>
     <t>(600,408)</t>
+  </si>
+  <si>
+    <t>Type_Old</t>
+  </si>
+  <si>
+    <t>Cong_target</t>
+  </si>
+  <si>
+    <t>Incong_target</t>
+  </si>
+  <si>
+    <t>Cong_lure</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/marina_B.jpg</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/castle_B.jpg</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/pharmacy_B.jpg</t>
+  </si>
+  <si>
+    <t>Incong_lure</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/restaurant_B.jpg</t>
+  </si>
+  <si>
+    <t>(600,411)</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/road_B.jpg</t>
+  </si>
+  <si>
+    <t>new_lure</t>
   </si>
 </sst>
 </file>
@@ -1226,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z91"/>
+  <dimension ref="A1:AA105"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.1640625" style="2" customWidth="1"/>
@@ -1235,17 +1250,17 @@
     <col min="4" max="4" width="16.6640625" style="2" customWidth="1"/>
     <col min="5" max="5" width="40.1640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="20.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="15" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="39.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.33203125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="15.6640625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="16.5" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="10.83203125" style="2"/>
+    <col min="7" max="8" width="15" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="39.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="16.5" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1268,27 +1283,29 @@
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4"/>
       <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
       <c r="R1" s="4"/>
@@ -1300,8 +1317,9 @@
       <c r="X1" s="4"/>
       <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA1" s="4"/>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -1324,27 +1342,29 @@
         <v>19</v>
       </c>
       <c r="H2" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="J2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="L2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="M2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>2</v>
       </c>
-      <c r="O2" s="7"/>
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
@@ -1356,8 +1376,9 @@
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
       <c r="Z2" s="7"/>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA2" s="7"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -1380,27 +1401,29 @@
         <v>19</v>
       </c>
       <c r="H3" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="L3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="M3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="N3" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>2.0499999999999998</v>
       </c>
-      <c r="O3" s="7"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
@@ -1412,8 +1435,9 @@
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
       <c r="Z3" s="7"/>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA3" s="7"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -1436,27 +1460,29 @@
         <v>19</v>
       </c>
       <c r="H4" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="L4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="M4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="N4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>2.1</v>
       </c>
-      <c r="O4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
@@ -1468,8 +1494,9 @@
       <c r="X4" s="7"/>
       <c r="Y4" s="7"/>
       <c r="Z4" s="7"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA4" s="7"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -1492,27 +1519,29 @@
         <v>19</v>
       </c>
       <c r="H5" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="K5" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="L5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="M5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="N5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>2.15</v>
       </c>
-      <c r="O5" s="7"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
@@ -1524,8 +1553,9 @@
       <c r="X5" s="7"/>
       <c r="Y5" s="7"/>
       <c r="Z5" s="7"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA5" s="7"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -1548,27 +1578,29 @@
         <v>19</v>
       </c>
       <c r="H6" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="K6" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="L6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="M6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="N6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>2.2000000000000002</v>
       </c>
-      <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
@@ -1580,8 +1612,9 @@
       <c r="X6" s="7"/>
       <c r="Y6" s="7"/>
       <c r="Z6" s="7"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA6" s="7"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>6</v>
       </c>
@@ -1604,27 +1637,29 @@
         <v>19</v>
       </c>
       <c r="H7" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="J7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="K7" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="L7" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="M7" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="N7" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>2.25</v>
       </c>
-      <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
@@ -1636,8 +1671,9 @@
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
       <c r="Z7" s="7"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="7"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>7</v>
       </c>
@@ -1660,27 +1696,29 @@
         <v>19</v>
       </c>
       <c r="H8" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="J8" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="K8" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="L8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="M8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="N8" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>2.2999999999999998</v>
       </c>
-      <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
@@ -1692,8 +1730,9 @@
       <c r="X8" s="7"/>
       <c r="Y8" s="7"/>
       <c r="Z8" s="7"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="7"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>8</v>
       </c>
@@ -1716,27 +1755,29 @@
         <v>19</v>
       </c>
       <c r="H9" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="J9" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="K9" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="L9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L9" s="10" t="s">
+      <c r="M9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="N9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>2.35</v>
       </c>
-      <c r="O9" s="7"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
@@ -1748,8 +1789,9 @@
       <c r="X9" s="7"/>
       <c r="Y9" s="7"/>
       <c r="Z9" s="7"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="7"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>9</v>
       </c>
@@ -1772,27 +1814,29 @@
         <v>19</v>
       </c>
       <c r="H10" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="J10" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="K10" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="L10" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="M10" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="N10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>2.4</v>
       </c>
-      <c r="O10" s="7"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
@@ -1804,8 +1848,9 @@
       <c r="X10" s="7"/>
       <c r="Y10" s="7"/>
       <c r="Z10" s="7"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="7"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>10</v>
       </c>
@@ -1828,27 +1873,29 @@
         <v>19</v>
       </c>
       <c r="H11" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="J11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="K11" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="L11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="M11" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="N11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>2.4500000000000002</v>
       </c>
-      <c r="O11" s="7"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
@@ -1860,8 +1907,9 @@
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
       <c r="Z11" s="7"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="7"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>11</v>
       </c>
@@ -1884,27 +1932,29 @@
         <v>19</v>
       </c>
       <c r="H12" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="J12" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="K12" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="L12" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L12" s="10" t="s">
+      <c r="M12" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="11" t="s">
+      <c r="N12" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>2.5</v>
       </c>
-      <c r="O12" s="7"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
@@ -1916,8 +1966,9 @@
       <c r="X12" s="7"/>
       <c r="Y12" s="7"/>
       <c r="Z12" s="7"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="7"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>12</v>
       </c>
@@ -1940,27 +1991,29 @@
         <v>19</v>
       </c>
       <c r="H13" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="J13" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="K13" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="L13" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L13" s="10" t="s">
+      <c r="M13" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M13" s="11" t="s">
+      <c r="N13" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>2.5499999999999998</v>
       </c>
-      <c r="O13" s="7"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
@@ -1972,8 +2025,9 @@
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
       <c r="Z13" s="7"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="7"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>13</v>
       </c>
@@ -1996,27 +2050,29 @@
         <v>19</v>
       </c>
       <c r="H14" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="J14" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="K14" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="K14" s="10" t="s">
+      <c r="L14" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L14" s="10" t="s">
+      <c r="M14" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="N14" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>2.6</v>
       </c>
-      <c r="O14" s="7"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
@@ -2028,8 +2084,9 @@
       <c r="X14" s="7"/>
       <c r="Y14" s="7"/>
       <c r="Z14" s="7"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="7"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>14</v>
       </c>
@@ -2052,27 +2109,29 @@
         <v>19</v>
       </c>
       <c r="H15" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="J15" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="K15" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="K15" s="10" t="s">
+      <c r="L15" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L15" s="10" t="s">
+      <c r="M15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M15" s="11" t="s">
+      <c r="N15" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>2.65</v>
       </c>
-      <c r="O15" s="7"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
@@ -2084,8 +2143,9 @@
       <c r="X15" s="7"/>
       <c r="Y15" s="7"/>
       <c r="Z15" s="7"/>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="7"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>15</v>
       </c>
@@ -2108,27 +2168,29 @@
         <v>19</v>
       </c>
       <c r="H16" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="J16" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="K16" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="L16" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L16" s="10" t="s">
+      <c r="M16" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M16" s="11" t="s">
+      <c r="N16" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>2.7</v>
       </c>
-      <c r="O16" s="7"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
@@ -2140,8 +2202,9 @@
       <c r="X16" s="7"/>
       <c r="Y16" s="7"/>
       <c r="Z16" s="7"/>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="7"/>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>16</v>
       </c>
@@ -2164,27 +2227,29 @@
         <v>19</v>
       </c>
       <c r="H17" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="J17" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="K17" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="L17" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L17" s="10" t="s">
+      <c r="M17" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M17" s="11" t="s">
+      <c r="N17" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>2.75</v>
       </c>
-      <c r="O17" s="7"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
@@ -2196,8 +2261,9 @@
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
       <c r="Z17" s="7"/>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="7"/>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>17</v>
       </c>
@@ -2220,27 +2286,29 @@
         <v>19</v>
       </c>
       <c r="H18" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="J18" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="K18" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="L18" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L18" s="10" t="s">
+      <c r="M18" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M18" s="11" t="s">
+      <c r="N18" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>2.8</v>
       </c>
-      <c r="O18" s="7"/>
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
@@ -2252,8 +2320,9 @@
       <c r="X18" s="7"/>
       <c r="Y18" s="7"/>
       <c r="Z18" s="7"/>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="7"/>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>18</v>
       </c>
@@ -2276,27 +2345,29 @@
         <v>19</v>
       </c>
       <c r="H19" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I19" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="J19" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="K19" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="K19" s="10" t="s">
+      <c r="L19" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L19" s="10" t="s">
+      <c r="M19" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M19" s="11" t="s">
+      <c r="N19" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>2.85</v>
       </c>
-      <c r="O19" s="7"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
@@ -2308,8 +2379,9 @@
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
       <c r="Z19" s="7"/>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="7"/>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>19</v>
       </c>
@@ -2332,27 +2404,29 @@
         <v>19</v>
       </c>
       <c r="H20" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="J20" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="K20" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="K20" s="10" t="s">
+      <c r="L20" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L20" s="10" t="s">
+      <c r="M20" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M20" s="11" t="s">
+      <c r="N20" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>2.9</v>
       </c>
-      <c r="O20" s="7"/>
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
       <c r="R20" s="7"/>
@@ -2364,8 +2438,9 @@
       <c r="X20" s="7"/>
       <c r="Y20" s="7"/>
       <c r="Z20" s="7"/>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="7"/>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>20</v>
       </c>
@@ -2388,27 +2463,29 @@
         <v>19</v>
       </c>
       <c r="H21" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="J21" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="K21" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="K21" s="10" t="s">
+      <c r="L21" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L21" s="10" t="s">
+      <c r="M21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M21" s="11" t="s">
+      <c r="N21" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>2.95</v>
       </c>
-      <c r="O21" s="7"/>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
@@ -2420,8 +2497,9 @@
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
       <c r="Z21" s="7"/>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="7"/>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>21</v>
       </c>
@@ -2444,27 +2522,29 @@
         <v>19</v>
       </c>
       <c r="H22" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I22" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="J22" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="K22" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="K22" s="10" t="s">
+      <c r="L22" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L22" s="10" t="s">
+      <c r="M22" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M22" s="11" t="s">
+      <c r="N22" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>3</v>
       </c>
-      <c r="O22" s="7"/>
       <c r="P22" s="7"/>
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
@@ -2476,8 +2556,9 @@
       <c r="X22" s="7"/>
       <c r="Y22" s="7"/>
       <c r="Z22" s="7"/>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="7"/>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>22</v>
       </c>
@@ -2500,27 +2581,29 @@
         <v>19</v>
       </c>
       <c r="H23" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I23" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="J23" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="K23" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K23" s="10" t="s">
+      <c r="L23" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L23" s="10" t="s">
+      <c r="M23" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M23" s="11" t="s">
+      <c r="N23" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>3.05</v>
       </c>
-      <c r="O23" s="7"/>
       <c r="P23" s="7"/>
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
@@ -2532,8 +2615,9 @@
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
       <c r="Z23" s="7"/>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="7"/>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>23</v>
       </c>
@@ -2556,27 +2640,29 @@
         <v>19</v>
       </c>
       <c r="H24" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I24" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="J24" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="K24" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="K24" s="10" t="s">
+      <c r="L24" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L24" s="10" t="s">
+      <c r="M24" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="11" t="s">
+      <c r="N24" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>3.1</v>
       </c>
-      <c r="O24" s="7"/>
       <c r="P24" s="7"/>
       <c r="Q24" s="7"/>
       <c r="R24" s="7"/>
@@ -2588,8 +2674,9 @@
       <c r="X24" s="7"/>
       <c r="Y24" s="7"/>
       <c r="Z24" s="7"/>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="7"/>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>24</v>
       </c>
@@ -2612,27 +2699,29 @@
         <v>19</v>
       </c>
       <c r="H25" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I25" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="J25" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="K25" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="K25" s="10" t="s">
+      <c r="L25" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L25" s="10" t="s">
+      <c r="M25" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M25" s="11" t="s">
+      <c r="N25" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>3.15</v>
       </c>
-      <c r="O25" s="7"/>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
@@ -2644,8 +2733,9 @@
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
       <c r="Z25" s="7"/>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="7"/>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
         <v>25</v>
       </c>
@@ -2668,27 +2758,29 @@
         <v>19</v>
       </c>
       <c r="H26" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I26" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="J26" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="J26" s="8" t="s">
+      <c r="K26" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K26" s="10" t="s">
+      <c r="L26" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L26" s="10" t="s">
+      <c r="M26" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M26" s="11" t="s">
+      <c r="N26" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>3.2</v>
       </c>
-      <c r="O26" s="7"/>
       <c r="P26" s="7"/>
       <c r="Q26" s="7"/>
       <c r="R26" s="7"/>
@@ -2700,8 +2792,9 @@
       <c r="X26" s="7"/>
       <c r="Y26" s="7"/>
       <c r="Z26" s="7"/>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="7"/>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" s="7">
         <v>26</v>
       </c>
@@ -2724,27 +2817,29 @@
         <v>19</v>
       </c>
       <c r="H27" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I27" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I27" s="7" t="s">
+      <c r="J27" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="J27" s="8" t="s">
+      <c r="K27" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="K27" s="10" t="s">
+      <c r="L27" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L27" s="10" t="s">
+      <c r="M27" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M27" s="11" t="s">
+      <c r="N27" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>3.25</v>
       </c>
-      <c r="O27" s="7"/>
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
       <c r="R27" s="7"/>
@@ -2756,8 +2851,9 @@
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
       <c r="Z27" s="7"/>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="7"/>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
         <v>27</v>
       </c>
@@ -2780,27 +2876,29 @@
         <v>19</v>
       </c>
       <c r="H28" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I28" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="J28" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="J28" s="8" t="s">
+      <c r="K28" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="K28" s="10" t="s">
+      <c r="L28" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L28" s="10" t="s">
+      <c r="M28" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M28" s="11" t="s">
+      <c r="N28" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>2</v>
       </c>
-      <c r="O28" s="7"/>
       <c r="P28" s="7"/>
       <c r="Q28" s="7"/>
       <c r="R28" s="7"/>
@@ -2812,8 +2910,9 @@
       <c r="X28" s="7"/>
       <c r="Y28" s="7"/>
       <c r="Z28" s="7"/>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="7"/>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="7">
         <v>28</v>
       </c>
@@ -2836,27 +2935,29 @@
         <v>19</v>
       </c>
       <c r="H29" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I29" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I29" s="7" t="s">
+      <c r="J29" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="J29" s="8" t="s">
+      <c r="K29" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="K29" s="10" t="s">
+      <c r="L29" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L29" s="10" t="s">
+      <c r="M29" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M29" s="11" t="s">
+      <c r="N29" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>2.0499999999999998</v>
       </c>
-      <c r="O29" s="7"/>
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
@@ -2868,8 +2969,9 @@
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
       <c r="Z29" s="7"/>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="7"/>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" s="7">
         <v>29</v>
       </c>
@@ -2892,27 +2994,29 @@
         <v>19</v>
       </c>
       <c r="H30" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I30" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I30" s="7" t="s">
+      <c r="J30" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="J30" s="8" t="s">
+      <c r="K30" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="K30" s="10" t="s">
+      <c r="L30" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L30" s="10" t="s">
+      <c r="M30" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M30" s="11" t="s">
+      <c r="N30" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>2.1</v>
       </c>
-      <c r="O30" s="7"/>
       <c r="P30" s="7"/>
       <c r="Q30" s="7"/>
       <c r="R30" s="7"/>
@@ -2924,8 +3028,9 @@
       <c r="X30" s="7"/>
       <c r="Y30" s="7"/>
       <c r="Z30" s="7"/>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="7"/>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" s="7">
         <v>30</v>
       </c>
@@ -2948,27 +3053,29 @@
         <v>19</v>
       </c>
       <c r="H31" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I31" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I31" s="7" t="s">
+      <c r="J31" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="J31" s="8" t="s">
+      <c r="K31" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="K31" s="10" t="s">
+      <c r="L31" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L31" s="10" t="s">
+      <c r="M31" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M31" s="11" t="s">
+      <c r="N31" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>2.15</v>
       </c>
-      <c r="O31" s="7"/>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
@@ -2980,8 +3087,9 @@
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
       <c r="Z31" s="7"/>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="7"/>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
         <v>31</v>
       </c>
@@ -3004,27 +3112,29 @@
         <v>19</v>
       </c>
       <c r="H32" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I32" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I32" s="7" t="s">
+      <c r="J32" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J32" s="8" t="s">
+      <c r="K32" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="K32" s="10" t="s">
+      <c r="L32" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L32" s="10" t="s">
+      <c r="M32" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M32" s="10" t="s">
+      <c r="N32" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>2.2000000000000002</v>
       </c>
-      <c r="O32" s="7"/>
       <c r="P32" s="7"/>
       <c r="Q32" s="7"/>
       <c r="R32" s="7"/>
@@ -3036,8 +3146,9 @@
       <c r="X32" s="7"/>
       <c r="Y32" s="7"/>
       <c r="Z32" s="7"/>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="7"/>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="7">
         <v>32</v>
       </c>
@@ -3060,27 +3171,29 @@
         <v>19</v>
       </c>
       <c r="H33" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I33" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I33" s="7" t="s">
+      <c r="J33" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="K33" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K33" s="10" t="s">
+      <c r="L33" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="10" t="s">
+      <c r="M33" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M33" s="10" t="s">
+      <c r="N33" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>2.25</v>
       </c>
-      <c r="O33" s="7"/>
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
@@ -3092,8 +3205,9 @@
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
       <c r="Z33" s="7"/>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="7"/>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
         <v>33</v>
       </c>
@@ -3116,27 +3230,29 @@
         <v>19</v>
       </c>
       <c r="H34" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I34" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I34" s="7" t="s">
+      <c r="J34" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="J34" s="8" t="s">
+      <c r="K34" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K34" s="10" t="s">
+      <c r="L34" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L34" s="10" t="s">
+      <c r="M34" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M34" s="10" t="s">
+      <c r="N34" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>2.2999999999999998</v>
       </c>
-      <c r="O34" s="7"/>
       <c r="P34" s="7"/>
       <c r="Q34" s="7"/>
       <c r="R34" s="7"/>
@@ -3148,8 +3264,9 @@
       <c r="X34" s="7"/>
       <c r="Y34" s="7"/>
       <c r="Z34" s="7"/>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="7"/>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="7">
         <v>34</v>
       </c>
@@ -3172,27 +3289,29 @@
         <v>19</v>
       </c>
       <c r="H35" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I35" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I35" s="7" t="s">
+      <c r="J35" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="J35" s="8" t="s">
+      <c r="K35" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="K35" s="10" t="s">
+      <c r="L35" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="10" t="s">
+      <c r="M35" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M35" s="10" t="s">
+      <c r="N35" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>2.35</v>
       </c>
-      <c r="O35" s="7"/>
       <c r="P35" s="7"/>
       <c r="Q35" s="7"/>
       <c r="R35" s="7"/>
@@ -3204,8 +3323,9 @@
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
       <c r="Z35" s="7"/>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="7"/>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
         <v>35</v>
       </c>
@@ -3228,27 +3348,29 @@
         <v>19</v>
       </c>
       <c r="H36" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I36" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I36" s="7" t="s">
+      <c r="J36" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="J36" s="8" t="s">
+      <c r="K36" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="K36" s="10" t="s">
+      <c r="L36" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L36" s="10" t="s">
+      <c r="M36" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M36" s="10" t="s">
+      <c r="N36" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>2.4</v>
       </c>
-      <c r="O36" s="7"/>
       <c r="P36" s="7"/>
       <c r="Q36" s="7"/>
       <c r="R36" s="7"/>
@@ -3260,8 +3382,9 @@
       <c r="X36" s="7"/>
       <c r="Y36" s="7"/>
       <c r="Z36" s="7"/>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA36" s="7"/>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="7">
         <v>36</v>
       </c>
@@ -3284,27 +3407,29 @@
         <v>19</v>
       </c>
       <c r="H37" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I37" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I37" s="7" t="s">
+      <c r="J37" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="J37" s="8" t="s">
+      <c r="K37" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K37" s="10" t="s">
+      <c r="L37" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L37" s="10" t="s">
+      <c r="M37" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M37" s="10" t="s">
+      <c r="N37" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N37">
+      <c r="O37">
         <v>2.4500000000000002</v>
       </c>
-      <c r="O37" s="7"/>
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
       <c r="R37" s="7"/>
@@ -3316,8 +3441,9 @@
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
       <c r="Z37" s="7"/>
-    </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA37" s="7"/>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
         <v>37</v>
       </c>
@@ -3340,27 +3466,29 @@
         <v>19</v>
       </c>
       <c r="H38" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I38" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I38" s="7" t="s">
+      <c r="J38" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="J38" s="8" t="s">
+      <c r="K38" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="K38" s="10" t="s">
+      <c r="L38" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="10" t="s">
+      <c r="M38" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M38" s="10" t="s">
+      <c r="N38" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N38">
+      <c r="O38">
         <v>2.5</v>
       </c>
-      <c r="O38" s="7"/>
       <c r="P38" s="7"/>
       <c r="Q38" s="7"/>
       <c r="R38" s="7"/>
@@ -3372,8 +3500,9 @@
       <c r="X38" s="7"/>
       <c r="Y38" s="7"/>
       <c r="Z38" s="7"/>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="7"/>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" s="7">
         <v>38</v>
       </c>
@@ -3396,27 +3525,29 @@
         <v>19</v>
       </c>
       <c r="H39" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I39" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I39" s="7" t="s">
+      <c r="J39" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="J39" s="8" t="s">
+      <c r="K39" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="K39" s="10" t="s">
+      <c r="L39" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="10" t="s">
+      <c r="M39" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M39" s="10" t="s">
+      <c r="N39" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N39">
+      <c r="O39">
         <v>2.5499999999999998</v>
       </c>
-      <c r="O39" s="7"/>
       <c r="P39" s="7"/>
       <c r="Q39" s="7"/>
       <c r="R39" s="7"/>
@@ -3428,8 +3559,9 @@
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
       <c r="Z39" s="7"/>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="7"/>
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="7">
         <v>39</v>
       </c>
@@ -3452,27 +3584,29 @@
         <v>19</v>
       </c>
       <c r="H40" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I40" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I40" s="7" t="s">
+      <c r="J40" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="J40" s="8" t="s">
+      <c r="K40" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K40" s="10" t="s">
+      <c r="L40" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L40" s="10" t="s">
+      <c r="M40" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M40" s="10" t="s">
+      <c r="N40" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N40">
+      <c r="O40">
         <v>2.6</v>
       </c>
-      <c r="O40" s="7"/>
       <c r="P40" s="7"/>
       <c r="Q40" s="7"/>
       <c r="R40" s="7"/>
@@ -3484,8 +3618,9 @@
       <c r="X40" s="7"/>
       <c r="Y40" s="7"/>
       <c r="Z40" s="7"/>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="7"/>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" s="7">
         <v>40</v>
       </c>
@@ -3508,27 +3643,29 @@
         <v>19</v>
       </c>
       <c r="H41" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I41" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I41" s="7" t="s">
+      <c r="J41" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="J41" s="8" t="s">
+      <c r="K41" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="K41" s="10" t="s">
+      <c r="L41" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L41" s="10" t="s">
+      <c r="M41" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M41" s="10" t="s">
+      <c r="N41" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N41">
+      <c r="O41">
         <v>2.65</v>
       </c>
-      <c r="O41" s="7"/>
       <c r="P41" s="7"/>
       <c r="Q41" s="7"/>
       <c r="R41" s="7"/>
@@ -3540,8 +3677,9 @@
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
       <c r="Z41" s="7"/>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="7"/>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
         <v>41</v>
       </c>
@@ -3564,27 +3702,29 @@
         <v>19</v>
       </c>
       <c r="H42" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I42" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I42" s="7" t="s">
+      <c r="J42" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J42" s="8" t="s">
+      <c r="K42" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K42" s="10" t="s">
+      <c r="L42" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L42" s="10" t="s">
+      <c r="M42" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M42" s="10" t="s">
+      <c r="N42" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N42">
+      <c r="O42">
         <v>2.7</v>
       </c>
-      <c r="O42" s="7"/>
       <c r="P42" s="7"/>
       <c r="Q42" s="7"/>
       <c r="R42" s="7"/>
@@ -3596,8 +3736,9 @@
       <c r="X42" s="7"/>
       <c r="Y42" s="7"/>
       <c r="Z42" s="7"/>
-    </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="7"/>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="7">
         <v>42</v>
       </c>
@@ -3620,27 +3761,29 @@
         <v>19</v>
       </c>
       <c r="H43" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I43" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I43" s="7" t="s">
+      <c r="J43" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J43" s="8" t="s">
+      <c r="K43" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="K43" s="10" t="s">
+      <c r="L43" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L43" s="10" t="s">
+      <c r="M43" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M43" s="10" t="s">
+      <c r="N43" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N43">
+      <c r="O43">
         <v>2.75</v>
       </c>
-      <c r="O43" s="7"/>
       <c r="P43" s="7"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="7"/>
@@ -3652,8 +3795,9 @@
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
       <c r="Z43" s="7"/>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="7"/>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" s="7">
         <v>43</v>
       </c>
@@ -3676,27 +3820,29 @@
         <v>19</v>
       </c>
       <c r="H44" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I44" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I44" s="7" t="s">
+      <c r="J44" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="J44" s="8" t="s">
+      <c r="K44" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="K44" s="10" t="s">
+      <c r="L44" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L44" s="10" t="s">
+      <c r="M44" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M44" s="10" t="s">
+      <c r="N44" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N44">
+      <c r="O44">
         <v>2.8</v>
       </c>
-      <c r="O44" s="7"/>
       <c r="P44" s="7"/>
       <c r="Q44" s="7"/>
       <c r="R44" s="7"/>
@@ -3708,8 +3854,9 @@
       <c r="X44" s="7"/>
       <c r="Y44" s="7"/>
       <c r="Z44" s="7"/>
-    </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="7"/>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45" s="7">
         <v>44</v>
       </c>
@@ -3732,27 +3879,29 @@
         <v>19</v>
       </c>
       <c r="H45" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I45" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I45" s="7" t="s">
+      <c r="J45" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="J45" s="8" t="s">
+      <c r="K45" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="K45" s="10" t="s">
+      <c r="L45" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="10" t="s">
+      <c r="M45" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M45" s="10" t="s">
+      <c r="N45" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N45">
+      <c r="O45">
         <v>2.85</v>
       </c>
-      <c r="O45" s="7"/>
       <c r="P45" s="7"/>
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
@@ -3764,8 +3913,9 @@
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
       <c r="Z45" s="7"/>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="7"/>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46" s="7">
         <v>45</v>
       </c>
@@ -3788,27 +3938,29 @@
         <v>19</v>
       </c>
       <c r="H46" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I46" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I46" s="7" t="s">
+      <c r="J46" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="J46" s="8" t="s">
+      <c r="K46" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="K46" s="10" t="s">
+      <c r="L46" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L46" s="10" t="s">
+      <c r="M46" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M46" s="10" t="s">
+      <c r="N46" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N46">
+      <c r="O46">
         <v>2.9</v>
       </c>
-      <c r="O46" s="7"/>
       <c r="P46" s="7"/>
       <c r="Q46" s="7"/>
       <c r="R46" s="7"/>
@@ -3820,8 +3972,9 @@
       <c r="X46" s="7"/>
       <c r="Y46" s="7"/>
       <c r="Z46" s="7"/>
-    </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="7"/>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47" s="7">
         <v>46</v>
       </c>
@@ -3844,27 +3997,29 @@
         <v>19</v>
       </c>
       <c r="H47" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I47" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I47" s="7" t="s">
+      <c r="J47" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="J47" s="8" t="s">
+      <c r="K47" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="K47" s="10" t="s">
+      <c r="L47" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L47" s="10" t="s">
+      <c r="M47" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M47" s="10" t="s">
+      <c r="N47" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N47">
+      <c r="O47">
         <v>2.95</v>
       </c>
-      <c r="O47" s="7"/>
       <c r="P47" s="7"/>
       <c r="Q47" s="7"/>
       <c r="R47" s="7"/>
@@ -3876,8 +4031,9 @@
       <c r="X47" s="7"/>
       <c r="Y47" s="7"/>
       <c r="Z47" s="7"/>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="7"/>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48" s="7">
         <v>47</v>
       </c>
@@ -3900,27 +4056,29 @@
         <v>19</v>
       </c>
       <c r="H48" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I48" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I48" s="7" t="s">
+      <c r="J48" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="J48" s="8" t="s">
+      <c r="K48" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="K48" s="10" t="s">
+      <c r="L48" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L48" s="10" t="s">
+      <c r="M48" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M48" s="10" t="s">
+      <c r="N48" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N48">
+      <c r="O48">
         <v>3</v>
       </c>
-      <c r="O48" s="7"/>
       <c r="P48" s="7"/>
       <c r="Q48" s="7"/>
       <c r="R48" s="7"/>
@@ -3932,8 +4090,9 @@
       <c r="X48" s="7"/>
       <c r="Y48" s="7"/>
       <c r="Z48" s="7"/>
-    </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="7"/>
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49" s="7">
         <v>48</v>
       </c>
@@ -3956,27 +4115,29 @@
         <v>19</v>
       </c>
       <c r="H49" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I49" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I49" s="7" t="s">
+      <c r="J49" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="J49" s="8" t="s">
+      <c r="K49" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="K49" s="10" t="s">
+      <c r="L49" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L49" s="10" t="s">
+      <c r="M49" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M49" s="10" t="s">
+      <c r="N49" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N49">
+      <c r="O49">
         <v>3.05</v>
       </c>
-      <c r="O49" s="7"/>
       <c r="P49" s="7"/>
       <c r="Q49" s="7"/>
       <c r="R49" s="7"/>
@@ -3988,8 +4149,9 @@
       <c r="X49" s="7"/>
       <c r="Y49" s="7"/>
       <c r="Z49" s="7"/>
-    </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="7"/>
+    </row>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50" s="7">
         <v>49</v>
       </c>
@@ -4012,27 +4174,29 @@
         <v>19</v>
       </c>
       <c r="H50" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I50" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I50" s="7" t="s">
+      <c r="J50" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="J50" s="8" t="s">
+      <c r="K50" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K50" s="10" t="s">
+      <c r="L50" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L50" s="10" t="s">
+      <c r="M50" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M50" s="10" t="s">
+      <c r="N50" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N50">
+      <c r="O50">
         <v>3.1</v>
       </c>
-      <c r="O50" s="7"/>
       <c r="P50" s="7"/>
       <c r="Q50" s="7"/>
       <c r="R50" s="7"/>
@@ -4044,8 +4208,9 @@
       <c r="X50" s="7"/>
       <c r="Y50" s="7"/>
       <c r="Z50" s="7"/>
-    </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="7"/>
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51" s="7">
         <v>50</v>
       </c>
@@ -4068,27 +4233,29 @@
         <v>19</v>
       </c>
       <c r="H51" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I51" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I51" s="7" t="s">
+      <c r="J51" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="J51" s="8" t="s">
+      <c r="K51" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="K51" s="10" t="s">
+      <c r="L51" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L51" s="10" t="s">
+      <c r="M51" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M51" s="10" t="s">
+      <c r="N51" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N51">
+      <c r="O51">
         <v>3.15</v>
       </c>
-      <c r="O51" s="7"/>
       <c r="P51" s="7"/>
       <c r="Q51" s="7"/>
       <c r="R51" s="7"/>
@@ -4100,8 +4267,9 @@
       <c r="X51" s="7"/>
       <c r="Y51" s="7"/>
       <c r="Z51" s="7"/>
-    </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="7"/>
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A52" s="7">
         <v>51</v>
       </c>
@@ -4124,27 +4292,29 @@
         <v>19</v>
       </c>
       <c r="H52" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I52" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I52" s="7" t="s">
+      <c r="J52" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="J52" s="8" t="s">
+      <c r="K52" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="K52" s="10" t="s">
+      <c r="L52" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L52" s="10" t="s">
+      <c r="M52" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M52" s="10" t="s">
+      <c r="N52" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N52">
+      <c r="O52">
         <v>3.2</v>
       </c>
-      <c r="O52" s="7"/>
       <c r="P52" s="7"/>
       <c r="Q52" s="7"/>
       <c r="R52" s="7"/>
@@ -4156,8 +4326,9 @@
       <c r="X52" s="7"/>
       <c r="Y52" s="7"/>
       <c r="Z52" s="7"/>
-    </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="7"/>
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A53" s="7">
         <v>52</v>
       </c>
@@ -4180,27 +4351,29 @@
         <v>19</v>
       </c>
       <c r="H53" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I53" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I53" s="7" t="s">
+      <c r="J53" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="J53" s="8" t="s">
+      <c r="K53" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="K53" s="10" t="s">
+      <c r="L53" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L53" s="10" t="s">
+      <c r="M53" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M53" s="10" t="s">
+      <c r="N53" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N53">
+      <c r="O53">
         <v>3.25</v>
       </c>
-      <c r="O53" s="7"/>
       <c r="P53" s="7"/>
       <c r="Q53" s="7"/>
       <c r="R53" s="7"/>
@@ -4212,8 +4385,9 @@
       <c r="X53" s="7"/>
       <c r="Y53" s="7"/>
       <c r="Z53" s="7"/>
-    </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="7"/>
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A54" s="7">
         <v>53</v>
       </c>
@@ -4236,27 +4410,29 @@
         <v>19</v>
       </c>
       <c r="H54" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I54" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I54" s="7" t="s">
+      <c r="J54" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="J54" s="8" t="s">
+      <c r="K54" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="K54" s="10" t="s">
+      <c r="L54" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L54" s="10" t="s">
+      <c r="M54" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M54" s="10" t="s">
+      <c r="N54" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N54">
+      <c r="O54">
         <v>2</v>
       </c>
-      <c r="O54" s="7"/>
       <c r="P54" s="7"/>
       <c r="Q54" s="7"/>
       <c r="R54" s="7"/>
@@ -4268,8 +4444,9 @@
       <c r="X54" s="7"/>
       <c r="Y54" s="7"/>
       <c r="Z54" s="7"/>
-    </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="7"/>
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55" s="7">
         <v>54</v>
       </c>
@@ -4292,27 +4469,29 @@
         <v>19</v>
       </c>
       <c r="H55" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I55" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I55" s="7" t="s">
+      <c r="J55" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="J55" s="8" t="s">
+      <c r="K55" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="K55" s="10" t="s">
+      <c r="L55" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L55" s="10" t="s">
+      <c r="M55" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M55" s="10" t="s">
+      <c r="N55" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N55">
+      <c r="O55">
         <v>2.0499999999999998</v>
       </c>
-      <c r="O55" s="7"/>
       <c r="P55" s="7"/>
       <c r="Q55" s="7"/>
       <c r="R55" s="7"/>
@@ -4324,8 +4503,9 @@
       <c r="X55" s="7"/>
       <c r="Y55" s="7"/>
       <c r="Z55" s="7"/>
-    </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="7"/>
+    </row>
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56" s="7">
         <v>55</v>
       </c>
@@ -4348,27 +4528,29 @@
         <v>19</v>
       </c>
       <c r="H56" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I56" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I56" s="7" t="s">
+      <c r="J56" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="J56" s="8" t="s">
+      <c r="K56" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="K56" s="10" t="s">
+      <c r="L56" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L56" s="10" t="s">
+      <c r="M56" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M56" s="10" t="s">
+      <c r="N56" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N56">
+      <c r="O56">
         <v>2.1</v>
       </c>
-      <c r="O56" s="7"/>
       <c r="P56" s="7"/>
       <c r="Q56" s="7"/>
       <c r="R56" s="7"/>
@@ -4380,8 +4562,9 @@
       <c r="X56" s="7"/>
       <c r="Y56" s="7"/>
       <c r="Z56" s="7"/>
-    </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="7"/>
+    </row>
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A57" s="7">
         <v>56</v>
       </c>
@@ -4404,27 +4587,29 @@
         <v>19</v>
       </c>
       <c r="H57" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I57" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I57" s="7" t="s">
+      <c r="J57" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="J57" s="8" t="s">
+      <c r="K57" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="K57" s="10" t="s">
+      <c r="L57" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L57" s="10" t="s">
+      <c r="M57" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M57" s="10" t="s">
+      <c r="N57" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N57">
+      <c r="O57">
         <v>2.15</v>
       </c>
-      <c r="O57" s="7"/>
       <c r="P57" s="7"/>
       <c r="Q57" s="7"/>
       <c r="R57" s="7"/>
@@ -4436,8 +4621,9 @@
       <c r="X57" s="7"/>
       <c r="Y57" s="7"/>
       <c r="Z57" s="7"/>
-    </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="7"/>
+    </row>
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58" s="7">
         <v>57</v>
       </c>
@@ -4460,27 +4646,29 @@
         <v>19</v>
       </c>
       <c r="H58" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I58" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I58" s="7" t="s">
+      <c r="J58" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="J58" s="8" t="s">
+      <c r="K58" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="K58" s="10" t="s">
+      <c r="L58" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L58" s="10" t="s">
+      <c r="M58" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M58" s="10" t="s">
+      <c r="N58" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N58">
+      <c r="O58">
         <v>2.2000000000000002</v>
       </c>
-      <c r="O58" s="7"/>
       <c r="P58" s="7"/>
       <c r="Q58" s="7"/>
       <c r="R58" s="7"/>
@@ -4492,8 +4680,9 @@
       <c r="X58" s="7"/>
       <c r="Y58" s="7"/>
       <c r="Z58" s="7"/>
-    </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="7"/>
+    </row>
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59" s="7">
         <v>58</v>
       </c>
@@ -4516,27 +4705,29 @@
         <v>19</v>
       </c>
       <c r="H59" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I59" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I59" s="7" t="s">
+      <c r="J59" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="J59" s="8" t="s">
+      <c r="K59" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="K59" s="10" t="s">
+      <c r="L59" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L59" s="10" t="s">
+      <c r="M59" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M59" s="10" t="s">
+      <c r="N59" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N59">
+      <c r="O59">
         <v>2.25</v>
       </c>
-      <c r="O59" s="7"/>
       <c r="P59" s="7"/>
       <c r="Q59" s="7"/>
       <c r="R59" s="7"/>
@@ -4548,8 +4739,9 @@
       <c r="X59" s="7"/>
       <c r="Y59" s="7"/>
       <c r="Z59" s="7"/>
-    </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="7"/>
+    </row>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60" s="7">
         <v>59</v>
       </c>
@@ -4572,27 +4764,29 @@
         <v>19</v>
       </c>
       <c r="H60" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I60" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I60" s="7" t="s">
+      <c r="J60" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="J60" s="8" t="s">
+      <c r="K60" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K60" s="10" t="s">
+      <c r="L60" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L60" s="10" t="s">
+      <c r="M60" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M60" s="10" t="s">
+      <c r="N60" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N60">
+      <c r="O60">
         <v>2.2999999999999998</v>
       </c>
-      <c r="O60" s="7"/>
       <c r="P60" s="7"/>
       <c r="Q60" s="7"/>
       <c r="R60" s="7"/>
@@ -4604,8 +4798,9 @@
       <c r="X60" s="7"/>
       <c r="Y60" s="7"/>
       <c r="Z60" s="7"/>
-    </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="7"/>
+    </row>
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A61" s="7">
         <v>60</v>
       </c>
@@ -4628,27 +4823,29 @@
         <v>19</v>
       </c>
       <c r="H61" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I61" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I61" s="7" t="s">
+      <c r="J61" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="J61" s="8" t="s">
+      <c r="K61" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="K61" s="10" t="s">
+      <c r="L61" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L61" s="10" t="s">
+      <c r="M61" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M61" s="10" t="s">
+      <c r="N61" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="N61">
+      <c r="O61">
         <v>2.35</v>
       </c>
-      <c r="O61" s="7"/>
       <c r="P61" s="7"/>
       <c r="Q61" s="7"/>
       <c r="R61" s="7"/>
@@ -4660,8 +4857,9 @@
       <c r="X61" s="7"/>
       <c r="Y61" s="7"/>
       <c r="Z61" s="7"/>
-    </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="7"/>
+    </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A62" s="7">
         <v>61</v>
       </c>
@@ -4680,17 +4878,19 @@
         <v>219</v>
       </c>
       <c r="H62" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="I62" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I62" s="7"/>
       <c r="J62" s="7"/>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
       <c r="M62" s="7"/>
-      <c r="N62">
+      <c r="N62" s="7"/>
+      <c r="O62">
         <v>2.15</v>
       </c>
-      <c r="O62" s="7"/>
       <c r="P62" s="7"/>
       <c r="Q62" s="7"/>
       <c r="R62" s="7"/>
@@ -4702,8 +4902,9 @@
       <c r="X62" s="7"/>
       <c r="Y62" s="7"/>
       <c r="Z62" s="7"/>
-    </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="7"/>
+    </row>
+    <row r="63" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A63" s="7">
         <v>62</v>
       </c>
@@ -4722,17 +4923,19 @@
         <v>219</v>
       </c>
       <c r="H63" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="I63" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I63" s="7"/>
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
       <c r="M63" s="7"/>
-      <c r="N63">
+      <c r="N63" s="7"/>
+      <c r="O63">
         <v>2.2000000000000002</v>
       </c>
-      <c r="O63" s="7"/>
       <c r="P63" s="7"/>
       <c r="Q63" s="7"/>
       <c r="R63" s="7"/>
@@ -4744,8 +4947,9 @@
       <c r="X63" s="7"/>
       <c r="Y63" s="7"/>
       <c r="Z63" s="7"/>
-    </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="7"/>
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A64" s="7">
         <v>63</v>
       </c>
@@ -4764,17 +4968,19 @@
         <v>219</v>
       </c>
       <c r="H64" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="I64" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I64" s="7"/>
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c r="M64" s="7"/>
-      <c r="N64">
+      <c r="N64" s="7"/>
+      <c r="O64">
         <v>2.25</v>
       </c>
-      <c r="O64" s="7"/>
       <c r="P64" s="7"/>
       <c r="Q64" s="7"/>
       <c r="R64" s="7"/>
@@ -4786,8 +4992,9 @@
       <c r="X64" s="7"/>
       <c r="Y64" s="7"/>
       <c r="Z64" s="7"/>
-    </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="7"/>
+    </row>
+    <row r="65" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A65" s="7">
         <v>64</v>
       </c>
@@ -4806,17 +5013,19 @@
         <v>219</v>
       </c>
       <c r="H65" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="I65" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I65" s="7"/>
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
       <c r="M65" s="7"/>
-      <c r="N65">
+      <c r="N65" s="7"/>
+      <c r="O65">
         <v>2.2999999999999998</v>
       </c>
-      <c r="O65" s="7"/>
       <c r="P65" s="7"/>
       <c r="Q65" s="7"/>
       <c r="R65" s="7"/>
@@ -4828,8 +5037,9 @@
       <c r="X65" s="7"/>
       <c r="Y65" s="7"/>
       <c r="Z65" s="7"/>
-    </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="7"/>
+    </row>
+    <row r="66" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A66" s="7">
         <v>65</v>
       </c>
@@ -4848,17 +5058,19 @@
         <v>219</v>
       </c>
       <c r="H66" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="I66" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I66" s="7"/>
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
       <c r="M66" s="7"/>
-      <c r="N66">
+      <c r="N66" s="7"/>
+      <c r="O66">
         <v>2.35</v>
       </c>
-      <c r="O66" s="7"/>
       <c r="P66" s="7"/>
       <c r="Q66" s="7"/>
       <c r="R66" s="7"/>
@@ -4870,13 +5082,14 @@
       <c r="X66" s="7"/>
       <c r="Y66" s="7"/>
       <c r="Z66" s="7"/>
-    </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="7"/>
+    </row>
+    <row r="67" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A67" s="7">
         <v>66</v>
       </c>
-      <c r="B67" s="7" t="s">
-        <v>226</v>
+      <c r="B67" s="2" t="s">
+        <v>259</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>37</v>
@@ -4890,17 +5103,19 @@
         <v>219</v>
       </c>
       <c r="H67" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="I67" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I67" s="7"/>
       <c r="J67" s="7"/>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
       <c r="M67" s="7"/>
-      <c r="N67">
+      <c r="N67" s="7"/>
+      <c r="O67">
         <v>2.4</v>
       </c>
-      <c r="O67" s="7"/>
       <c r="P67" s="7"/>
       <c r="Q67" s="7"/>
       <c r="R67" s="7"/>
@@ -4912,16 +5127,17 @@
       <c r="X67" s="7"/>
       <c r="Y67" s="7"/>
       <c r="Z67" s="7"/>
-    </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="7"/>
+    </row>
+    <row r="68" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A68" s="7">
         <v>67</v>
       </c>
-      <c r="B68" s="7" t="s">
-        <v>227</v>
+      <c r="B68" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>228</v>
+        <v>37</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>218</v>
@@ -4932,17 +5148,19 @@
         <v>219</v>
       </c>
       <c r="H68" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="I68" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I68" s="7"/>
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
       <c r="M68" s="7"/>
-      <c r="N68">
+      <c r="N68" s="7"/>
+      <c r="O68">
         <v>2.4500000000000002</v>
       </c>
-      <c r="O68" s="7"/>
       <c r="P68" s="7"/>
       <c r="Q68" s="7"/>
       <c r="R68" s="7"/>
@@ -4954,16 +5172,17 @@
       <c r="X68" s="7"/>
       <c r="Y68" s="7"/>
       <c r="Z68" s="7"/>
-    </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="7"/>
+    </row>
+    <row r="69" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A69" s="7">
         <v>68</v>
       </c>
-      <c r="B69" s="7" t="s">
-        <v>229</v>
+      <c r="B69" s="2" t="s">
+        <v>261</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>218</v>
@@ -4974,17 +5193,19 @@
         <v>219</v>
       </c>
       <c r="H69" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="I69" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I69" s="7"/>
       <c r="J69" s="7"/>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c r="M69" s="7"/>
-      <c r="N69">
+      <c r="N69" s="7"/>
+      <c r="O69">
         <v>2.5</v>
       </c>
-      <c r="O69" s="7"/>
       <c r="P69" s="7"/>
       <c r="Q69" s="7"/>
       <c r="R69" s="7"/>
@@ -4996,13 +5217,14 @@
       <c r="X69" s="7"/>
       <c r="Y69" s="7"/>
       <c r="Z69" s="7"/>
-    </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="7"/>
+    </row>
+    <row r="70" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A70" s="7">
         <v>69</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>37</v>
@@ -5016,17 +5238,19 @@
         <v>219</v>
       </c>
       <c r="H70" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="I70" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I70" s="7"/>
       <c r="J70" s="7"/>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c r="M70" s="7"/>
-      <c r="N70">
+      <c r="N70" s="7"/>
+      <c r="O70">
         <v>2.5499999999999998</v>
       </c>
-      <c r="O70" s="7"/>
       <c r="P70" s="7"/>
       <c r="Q70" s="7"/>
       <c r="R70" s="7"/>
@@ -5038,16 +5262,17 @@
       <c r="X70" s="7"/>
       <c r="Y70" s="7"/>
       <c r="Z70" s="7"/>
-    </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="7"/>
+    </row>
+    <row r="71" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A71" s="7">
         <v>70</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>37</v>
+        <v>228</v>
       </c>
       <c r="D71" s="13" t="s">
         <v>218</v>
@@ -5058,17 +5283,19 @@
         <v>219</v>
       </c>
       <c r="H71" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="I71" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I71" s="7"/>
       <c r="J71" s="7"/>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c r="M71" s="7"/>
-      <c r="N71">
+      <c r="N71" s="7"/>
+      <c r="O71">
         <v>2.6</v>
       </c>
-      <c r="O71" s="7"/>
       <c r="P71" s="7"/>
       <c r="Q71" s="7"/>
       <c r="R71" s="7"/>
@@ -5080,16 +5307,17 @@
       <c r="X71" s="7"/>
       <c r="Y71" s="7"/>
       <c r="Z71" s="7"/>
-    </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="7"/>
+    </row>
+    <row r="72" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A72" s="7">
         <v>71</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>223</v>
+        <v>37</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>218</v>
@@ -5100,17 +5328,19 @@
         <v>219</v>
       </c>
       <c r="H72" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="I72" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I72" s="7"/>
       <c r="J72" s="7"/>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
       <c r="M72" s="7"/>
-      <c r="N72">
+      <c r="N72" s="7"/>
+      <c r="O72">
         <v>2.65</v>
       </c>
-      <c r="O72" s="7"/>
       <c r="P72" s="7"/>
       <c r="Q72" s="7"/>
       <c r="R72" s="7"/>
@@ -5122,16 +5352,17 @@
       <c r="X72" s="7"/>
       <c r="Y72" s="7"/>
       <c r="Z72" s="7"/>
-    </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="7"/>
+    </row>
+    <row r="73" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A73" s="7">
         <v>72</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D73" s="13" t="s">
         <v>218</v>
@@ -5142,17 +5373,19 @@
         <v>219</v>
       </c>
       <c r="H73" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="I73" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I73" s="7"/>
       <c r="J73" s="7"/>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c r="M73" s="7"/>
-      <c r="N73">
+      <c r="N73" s="7"/>
+      <c r="O73">
         <v>2.7</v>
       </c>
-      <c r="O73" s="7"/>
       <c r="P73" s="7"/>
       <c r="Q73" s="7"/>
       <c r="R73" s="7"/>
@@ -5164,16 +5397,17 @@
       <c r="X73" s="7"/>
       <c r="Y73" s="7"/>
       <c r="Z73" s="7"/>
-    </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="7"/>
+    </row>
+    <row r="74" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A74" s="7">
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>235</v>
+        <v>37</v>
       </c>
       <c r="D74" s="13" t="s">
         <v>218</v>
@@ -5184,17 +5418,19 @@
         <v>219</v>
       </c>
       <c r="H74" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="I74" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I74" s="7"/>
       <c r="J74" s="7"/>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c r="M74" s="7"/>
-      <c r="N74">
+      <c r="N74" s="7"/>
+      <c r="O74">
         <v>2.75</v>
       </c>
-      <c r="O74" s="7"/>
       <c r="P74" s="7"/>
       <c r="Q74" s="7"/>
       <c r="R74" s="7"/>
@@ -5206,16 +5442,17 @@
       <c r="X74" s="7"/>
       <c r="Y74" s="7"/>
       <c r="Z74" s="7"/>
-    </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="7"/>
+    </row>
+    <row r="75" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A75" s="7">
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="D75" s="13" t="s">
         <v>218</v>
@@ -5226,17 +5463,19 @@
         <v>219</v>
       </c>
       <c r="H75" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="I75" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I75" s="7"/>
       <c r="J75" s="7"/>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c r="M75" s="7"/>
-      <c r="N75">
+      <c r="N75" s="7"/>
+      <c r="O75">
         <v>2.8</v>
       </c>
-      <c r="O75" s="7"/>
       <c r="P75" s="7"/>
       <c r="Q75" s="7"/>
       <c r="R75" s="7"/>
@@ -5248,16 +5487,17 @@
       <c r="X75" s="7"/>
       <c r="Y75" s="7"/>
       <c r="Z75" s="7"/>
-    </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="7"/>
+    </row>
+    <row r="76" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A76" s="7">
         <v>75</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>110</v>
+        <v>264</v>
       </c>
       <c r="D76" s="13" t="s">
         <v>218</v>
@@ -5268,17 +5508,19 @@
         <v>219</v>
       </c>
       <c r="H76" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="I76" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I76" s="7"/>
       <c r="J76" s="7"/>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c r="M76" s="7"/>
-      <c r="N76">
+      <c r="N76" s="7"/>
+      <c r="O76">
         <v>2.85</v>
       </c>
-      <c r="O76" s="7"/>
       <c r="P76" s="7"/>
       <c r="Q76" s="7"/>
       <c r="R76" s="7"/>
@@ -5290,16 +5532,17 @@
       <c r="X76" s="7"/>
       <c r="Y76" s="7"/>
       <c r="Z76" s="7"/>
-    </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="7"/>
+    </row>
+    <row r="77" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A77" s="7">
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>218</v>
@@ -5310,17 +5553,19 @@
         <v>219</v>
       </c>
       <c r="H77" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="I77" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I77" s="7"/>
       <c r="J77" s="7"/>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
       <c r="M77" s="7"/>
-      <c r="N77">
+      <c r="N77" s="7"/>
+      <c r="O77">
         <v>2.9</v>
       </c>
-      <c r="O77" s="7"/>
       <c r="P77" s="7"/>
       <c r="Q77" s="7"/>
       <c r="R77" s="7"/>
@@ -5332,16 +5577,17 @@
       <c r="X77" s="7"/>
       <c r="Y77" s="7"/>
       <c r="Z77" s="7"/>
-    </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="7"/>
+    </row>
+    <row r="78" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A78" s="7">
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>218</v>
@@ -5352,17 +5598,19 @@
         <v>219</v>
       </c>
       <c r="H78" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="I78" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I78" s="7"/>
       <c r="J78" s="7"/>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
       <c r="M78" s="7"/>
-      <c r="N78">
+      <c r="N78" s="7"/>
+      <c r="O78">
         <v>2.95</v>
       </c>
-      <c r="O78" s="7"/>
       <c r="P78" s="7"/>
       <c r="Q78" s="7"/>
       <c r="R78" s="7"/>
@@ -5374,16 +5622,17 @@
       <c r="X78" s="7"/>
       <c r="Y78" s="7"/>
       <c r="Z78" s="7"/>
-    </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA78" s="7"/>
+    </row>
+    <row r="79" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A79" s="7">
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D79" s="13" t="s">
         <v>218</v>
@@ -5394,17 +5643,19 @@
         <v>219</v>
       </c>
       <c r="H79" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="I79" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I79" s="7"/>
       <c r="J79" s="7"/>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c r="M79" s="7"/>
-      <c r="N79">
+      <c r="N79" s="7"/>
+      <c r="O79">
         <v>3</v>
       </c>
-      <c r="O79" s="7"/>
       <c r="P79" s="7"/>
       <c r="Q79" s="7"/>
       <c r="R79" s="7"/>
@@ -5416,16 +5667,17 @@
       <c r="X79" s="7"/>
       <c r="Y79" s="7"/>
       <c r="Z79" s="7"/>
-    </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA79" s="7"/>
+    </row>
+    <row r="80" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A80" s="7">
         <v>79</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D80" s="13" t="s">
         <v>218</v>
@@ -5436,17 +5688,19 @@
         <v>219</v>
       </c>
       <c r="H80" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="I80" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I80" s="7"/>
       <c r="J80" s="7"/>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c r="M80" s="7"/>
-      <c r="N80">
+      <c r="N80" s="7"/>
+      <c r="O80">
         <v>3.05</v>
       </c>
-      <c r="O80" s="7"/>
       <c r="P80" s="7"/>
       <c r="Q80" s="7"/>
       <c r="R80" s="7"/>
@@ -5458,13 +5712,14 @@
       <c r="X80" s="7"/>
       <c r="Y80" s="7"/>
       <c r="Z80" s="7"/>
-    </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="7"/>
+    </row>
+    <row r="81" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A81" s="7">
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>37</v>
@@ -5478,17 +5733,19 @@
         <v>219</v>
       </c>
       <c r="H81" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="I81" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I81" s="7"/>
       <c r="J81" s="7"/>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c r="M81" s="7"/>
-      <c r="N81">
+      <c r="N81" s="7"/>
+      <c r="O81">
         <v>3.1</v>
       </c>
-      <c r="O81" s="7"/>
       <c r="P81" s="7"/>
       <c r="Q81" s="7"/>
       <c r="R81" s="7"/>
@@ -5500,16 +5757,17 @@
       <c r="X81" s="7"/>
       <c r="Y81" s="7"/>
       <c r="Z81" s="7"/>
-    </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="7"/>
+    </row>
+    <row r="82" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A82" s="7">
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>218</v>
@@ -5520,17 +5778,19 @@
         <v>219</v>
       </c>
       <c r="H82" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="I82" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I82" s="7"/>
       <c r="J82" s="7"/>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
       <c r="M82" s="7"/>
-      <c r="N82">
+      <c r="N82" s="7"/>
+      <c r="O82">
         <v>3.15</v>
       </c>
-      <c r="O82" s="7"/>
       <c r="P82" s="7"/>
       <c r="Q82" s="7"/>
       <c r="R82" s="7"/>
@@ -5542,13 +5802,14 @@
       <c r="X82" s="7"/>
       <c r="Y82" s="7"/>
       <c r="Z82" s="7"/>
-    </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="7"/>
+    </row>
+    <row r="83" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A83" s="7">
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>27</v>
@@ -5562,17 +5823,19 @@
         <v>219</v>
       </c>
       <c r="H83" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="I83" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I83" s="7"/>
       <c r="J83" s="7"/>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
       <c r="M83" s="7"/>
-      <c r="N83">
+      <c r="N83" s="7"/>
+      <c r="O83">
         <v>3.2</v>
       </c>
-      <c r="O83" s="7"/>
       <c r="P83" s="7"/>
       <c r="Q83" s="7"/>
       <c r="R83" s="7"/>
@@ -5584,16 +5847,17 @@
       <c r="X83" s="7"/>
       <c r="Y83" s="7"/>
       <c r="Z83" s="7"/>
-    </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="7"/>
+    </row>
+    <row r="84" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A84" s="7">
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>218</v>
@@ -5604,17 +5868,19 @@
         <v>219</v>
       </c>
       <c r="H84" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="I84" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I84" s="7"/>
       <c r="J84" s="7"/>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
       <c r="M84" s="7"/>
-      <c r="N84">
+      <c r="N84" s="7"/>
+      <c r="O84">
         <v>3.25</v>
       </c>
-      <c r="O84" s="7"/>
       <c r="P84" s="7"/>
       <c r="Q84" s="7"/>
       <c r="R84" s="7"/>
@@ -5626,13 +5892,14 @@
       <c r="X84" s="7"/>
       <c r="Y84" s="7"/>
       <c r="Z84" s="7"/>
-    </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="7"/>
+    </row>
+    <row r="85" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A85" s="7">
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>216</v>
@@ -5646,17 +5913,19 @@
         <v>219</v>
       </c>
       <c r="H85" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="I85" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I85" s="7"/>
       <c r="J85" s="7"/>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c r="M85" s="7"/>
-      <c r="N85">
+      <c r="N85" s="7"/>
+      <c r="O85">
         <v>2</v>
       </c>
-      <c r="O85" s="7"/>
       <c r="P85" s="7"/>
       <c r="Q85" s="7"/>
       <c r="R85" s="7"/>
@@ -5668,13 +5937,14 @@
       <c r="X85" s="7"/>
       <c r="Y85" s="7"/>
       <c r="Z85" s="7"/>
-    </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="7"/>
+    </row>
+    <row r="86" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A86" s="7">
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>125</v>
@@ -5688,17 +5958,19 @@
         <v>219</v>
       </c>
       <c r="H86" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="I86" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I86" s="7"/>
       <c r="J86" s="7"/>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
       <c r="M86" s="7"/>
-      <c r="N86">
+      <c r="N86" s="7"/>
+      <c r="O86">
         <v>2.0499999999999998</v>
       </c>
-      <c r="O86" s="7"/>
       <c r="P86" s="7"/>
       <c r="Q86" s="7"/>
       <c r="R86" s="7"/>
@@ -5710,16 +5982,17 @@
       <c r="X86" s="7"/>
       <c r="Y86" s="7"/>
       <c r="Z86" s="7"/>
-    </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="7"/>
+    </row>
+    <row r="87" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A87" s="7">
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D87" s="13" t="s">
         <v>218</v>
@@ -5730,17 +6003,19 @@
         <v>219</v>
       </c>
       <c r="H87" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="I87" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I87" s="7"/>
       <c r="J87" s="7"/>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c r="M87" s="7"/>
-      <c r="N87">
+      <c r="N87" s="7"/>
+      <c r="O87">
         <v>2.1</v>
       </c>
-      <c r="O87" s="7"/>
       <c r="P87" s="7"/>
       <c r="Q87" s="7"/>
       <c r="R87" s="7"/>
@@ -5752,13 +6027,14 @@
       <c r="X87" s="7"/>
       <c r="Y87" s="7"/>
       <c r="Z87" s="7"/>
-    </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="7"/>
+    </row>
+    <row r="88" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A88" s="7">
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>65</v>
@@ -5772,17 +6048,19 @@
         <v>219</v>
       </c>
       <c r="H88" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="I88" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I88" s="7"/>
       <c r="J88" s="7"/>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c r="M88" s="7"/>
-      <c r="N88">
+      <c r="N88" s="7"/>
+      <c r="O88">
         <v>2.15</v>
       </c>
-      <c r="O88" s="7"/>
       <c r="P88" s="7"/>
       <c r="Q88" s="7"/>
       <c r="R88" s="7"/>
@@ -5794,16 +6072,17 @@
       <c r="X88" s="7"/>
       <c r="Y88" s="7"/>
       <c r="Z88" s="7"/>
-    </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="7"/>
+    </row>
+    <row r="89" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A89" s="7">
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>218</v>
@@ -5814,17 +6093,19 @@
         <v>219</v>
       </c>
       <c r="H89" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="I89" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I89" s="7"/>
       <c r="J89" s="7"/>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c r="M89" s="7"/>
-      <c r="N89">
+      <c r="N89" s="7"/>
+      <c r="O89">
         <v>2.2000000000000002</v>
       </c>
-      <c r="O89" s="7"/>
       <c r="P89" s="7"/>
       <c r="Q89" s="7"/>
       <c r="R89" s="7"/>
@@ -5836,13 +6117,14 @@
       <c r="X89" s="7"/>
       <c r="Y89" s="7"/>
       <c r="Z89" s="7"/>
-    </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="7"/>
+    </row>
+    <row r="90" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A90" s="7">
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>27</v>
@@ -5856,17 +6138,19 @@
         <v>219</v>
       </c>
       <c r="H90" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="I90" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I90" s="7"/>
       <c r="J90" s="7"/>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
       <c r="M90" s="7"/>
-      <c r="N90">
+      <c r="N90" s="7"/>
+      <c r="O90">
         <v>2.25</v>
       </c>
-      <c r="O90" s="7"/>
       <c r="P90" s="7"/>
       <c r="Q90" s="7"/>
       <c r="R90" s="7"/>
@@ -5878,16 +6162,17 @@
       <c r="X90" s="7"/>
       <c r="Y90" s="7"/>
       <c r="Z90" s="7"/>
-    </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="7"/>
+    </row>
+    <row r="91" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A91" s="7">
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="D91" s="13" t="s">
         <v>218</v>
@@ -5898,17 +6183,19 @@
         <v>219</v>
       </c>
       <c r="H91" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="I91" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I91" s="7"/>
       <c r="J91" s="7"/>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c r="M91" s="7"/>
-      <c r="N91">
+      <c r="N91" s="7"/>
+      <c r="O91">
         <v>2.2999999999999998</v>
       </c>
-      <c r="O91" s="7"/>
       <c r="P91" s="7"/>
       <c r="Q91" s="7"/>
       <c r="R91" s="7"/>
@@ -5920,6 +6207,27 @@
       <c r="X91" s="7"/>
       <c r="Y91" s="7"/>
       <c r="Z91" s="7"/>
+      <c r="AA91" s="7"/>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B101" s="7"/>
+      <c r="C101" s="8"/>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B102" s="7"/>
+      <c r="C102" s="8"/>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B103" s="7"/>
+      <c r="C103" s="8"/>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B104" s="7"/>
+      <c r="C104" s="8"/>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B105" s="7"/>
+      <c r="C105" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/encode_pairs.xlsx
+++ b/encode_pairs.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IBEB\Documents\GitHub\SEED\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vera/Documents/GitHub/SEED/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D976CD-797A-F242-8D09-94FC3640E606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="1120" windowWidth="24640" windowHeight="16880"/>
+    <workbookView xWindow="1160" yWindow="500" windowWidth="27640" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="263">
   <si>
     <t>Index</t>
   </si>
@@ -38,9 +40,6 @@
     <t>Object_Size</t>
   </si>
   <si>
-    <t>Condition_Old</t>
-  </si>
-  <si>
     <t>Correct_Key_Old</t>
   </si>
   <si>
@@ -719,27 +718,6 @@
     <t>Scenes_Dataset/field_B.jpg</t>
   </si>
   <si>
-    <t>Scenes_Dataset/underwater_A.jpg</t>
-  </si>
-  <si>
-    <t>Scenes_Dataset/cemetery_A.jpg</t>
-  </si>
-  <si>
-    <t>(600,452)</t>
-  </si>
-  <si>
-    <t>Scenes_Dataset/terrace_A.jpg</t>
-  </si>
-  <si>
-    <t>(600,451)</t>
-  </si>
-  <si>
-    <t>Scenes_Dataset/gymnasium_A.jpg</t>
-  </si>
-  <si>
-    <t>Scenes_Dataset/laboratory_A.jpg</t>
-  </si>
-  <si>
     <t>Scenes_Dataset/trash_A.jpg</t>
   </si>
   <si>
@@ -804,13 +782,40 @@
   </si>
   <si>
     <t>(600,408)</t>
+  </si>
+  <si>
+    <t>OldNew_Condition</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/marina_B.jpg</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/castle_B.jpg</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/pharmacy_B.jpg</t>
+  </si>
+  <si>
+    <t>Alternative_Congruent</t>
+  </si>
+  <si>
+    <t>Alternative_Incongruent</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/restaurant_B.jpg</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/road_B.jpg</t>
+  </si>
+  <si>
+    <t>(600,411)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -830,11 +835,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -846,30 +853,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -904,12 +935,32 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -918,10 +969,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -1201,71 +1252,74 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z91"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="36.10938" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16.10938" style="3" customWidth="1"/>
-    <col min="4" max="4" width="16.66406" style="2" customWidth="1"/>
-    <col min="5" max="5" width="40.10938" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.44141" style="2" customWidth="1"/>
-    <col min="7" max="7" width="15" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.66406" style="2" customWidth="1"/>
-    <col min="9" max="9" width="39.44141" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.33203" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14.66406" style="2" customWidth="1"/>
-    <col min="12" max="12" width="15.66406" style="2" customWidth="1"/>
-    <col min="13" max="13" width="16.44141" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="10.77734" style="2"/>
+    <col min="1" max="1" width="7.1640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="36.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.1640625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="40.1640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="39.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="16.5" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15.75">
+    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>13</v>
       </c>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
@@ -1280,45 +1334,45 @@
       <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="H2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="J2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>22</v>
-      </c>
       <c r="K2" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="N2">
         <v>2</v>
@@ -1336,45 +1390,45 @@
       <c r="Y2" s="7"/>
       <c r="Z2" s="7"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="F3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="8" t="s">
-        <v>29</v>
-      </c>
       <c r="K3" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="N3">
         <v>2.0499999999999998</v>
@@ -1392,48 +1446,48 @@
       <c r="Y3" s="7"/>
       <c r="Z3" s="7"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="H4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="7" t="s">
+      <c r="J4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="8" t="s">
-        <v>35</v>
-      </c>
       <c r="K4" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="N4">
-        <v>2.1000000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
@@ -1448,48 +1502,48 @@
       <c r="Y4" s="7"/>
       <c r="Z4" s="7"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="H5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="8" t="s">
-        <v>41</v>
-      </c>
       <c r="K5" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M5" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="N5">
-        <v>2.1499999999999999</v>
+        <v>2.15</v>
       </c>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
@@ -1504,45 +1558,45 @@
       <c r="Y5" s="7"/>
       <c r="Z5" s="7"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="G6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="7" t="s">
+      <c r="J6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="K6" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="N6">
         <v>2.2000000000000002</v>
@@ -1560,45 +1614,45 @@
       <c r="Y6" s="7"/>
       <c r="Z6" s="7"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="H7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="7" t="s">
+      <c r="J7" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="J7" s="8" t="s">
-        <v>52</v>
-      </c>
       <c r="K7" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="N7">
         <v>2.25</v>
@@ -1616,45 +1670,45 @@
       <c r="Y7" s="7"/>
       <c r="Z7" s="7"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="7" t="s">
+      <c r="G8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="H8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>56</v>
-      </c>
       <c r="J8" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="N8">
         <v>2.2999999999999998</v>
@@ -1672,48 +1726,48 @@
       <c r="Y8" s="7"/>
       <c r="Z8" s="7"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>19</v>
+      <c r="E9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="8" t="s">
-        <v>55</v>
-      </c>
       <c r="K9" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="N9">
-        <v>2.3500000000000001</v>
+        <v>2.35</v>
       </c>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
@@ -1728,48 +1782,48 @@
       <c r="Y9" s="7"/>
       <c r="Z9" s="7"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="7" t="s">
+      <c r="G10" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="H10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="7" t="s">
+      <c r="J10" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="8" t="s">
-        <v>63</v>
-      </c>
       <c r="K10" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M10" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="N10">
-        <v>2.3999999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
@@ -1784,45 +1838,45 @@
       <c r="Y10" s="7"/>
       <c r="Z10" s="7"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="F11" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="H11" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>61</v>
-      </c>
       <c r="K11" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="N11">
         <v>2.4500000000000002</v>
@@ -1840,45 +1894,45 @@
       <c r="Y11" s="7"/>
       <c r="Z11" s="7"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="7" t="s">
+      <c r="G12" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="7" t="s">
+      <c r="J12" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="J12" s="8" t="s">
-        <v>70</v>
-      </c>
       <c r="K12" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="N12">
         <v>2.5</v>
@@ -1896,45 +1950,45 @@
       <c r="Y12" s="7"/>
       <c r="Z12" s="7"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="7" t="s">
+      <c r="G13" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="7" t="s">
+      <c r="J13" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="J13" s="8" t="s">
-        <v>74</v>
-      </c>
       <c r="K13" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L13" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="N13">
         <v>2.5499999999999998</v>
@@ -1952,48 +2006,48 @@
       <c r="Y13" s="7"/>
       <c r="Z13" s="7"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="7" t="s">
+      <c r="G14" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="H14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I14" s="7" t="s">
+      <c r="J14" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="J14" s="8" t="s">
-        <v>80</v>
-      </c>
       <c r="K14" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L14" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M14" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="N14">
-        <v>2.6000000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
@@ -2008,48 +2062,48 @@
       <c r="Y14" s="7"/>
       <c r="Z14" s="7"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="F15" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="7" t="s">
+      <c r="G15" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="H15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>85</v>
-      </c>
       <c r="J15" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L15" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M15" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="N15">
-        <v>2.6499999999999999</v>
+        <v>2.65</v>
       </c>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
@@ -2064,48 +2118,48 @@
       <c r="Y15" s="7"/>
       <c r="Z15" s="7"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="7" t="s">
+      <c r="G16" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="H16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I16" s="7" t="s">
+      <c r="J16" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="J16" s="8" t="s">
-        <v>90</v>
-      </c>
       <c r="K16" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L16" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M16" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M16" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="N16">
-        <v>2.7000000000000002</v>
+        <v>2.7</v>
       </c>
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
@@ -2120,45 +2174,45 @@
       <c r="Y16" s="7"/>
       <c r="Z16" s="7"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="F17" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="7" t="s">
+      <c r="G17" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="H17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="G17" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>95</v>
-      </c>
       <c r="J17" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L17" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M17" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="N17">
         <v>2.75</v>
@@ -2176,48 +2230,48 @@
       <c r="Y17" s="7"/>
       <c r="Z17" s="7"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="F18" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="7" t="s">
+      <c r="G18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I18" s="7" t="s">
+      <c r="J18" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="J18" s="8" t="s">
-        <v>100</v>
-      </c>
       <c r="K18" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L18" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M18" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="N18">
-        <v>2.7999999999999998</v>
+        <v>2.8</v>
       </c>
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
@@ -2232,48 +2286,48 @@
       <c r="Y18" s="7"/>
       <c r="Z18" s="7"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="7" t="s">
+      <c r="G19" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I19" s="7" t="s">
+      <c r="J19" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="J19" s="8" t="s">
-        <v>104</v>
-      </c>
       <c r="K19" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L19" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M19" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="N19">
-        <v>2.8500000000000001</v>
+        <v>2.85</v>
       </c>
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
@@ -2288,48 +2342,48 @@
       <c r="Y19" s="7"/>
       <c r="Z19" s="7"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="F20" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D20" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" s="7" t="s">
+      <c r="G20" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="H20" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I20" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="J20" s="8" t="s">
-        <v>88</v>
-      </c>
       <c r="K20" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L20" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M20" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="N20">
-        <v>2.8999999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="O20" s="7"/>
       <c r="P20" s="7"/>
@@ -2344,48 +2398,48 @@
       <c r="Y20" s="7"/>
       <c r="Z20" s="7"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="F21" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I21" s="7" t="s">
+      <c r="J21" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="J21" s="8" t="s">
-        <v>112</v>
-      </c>
       <c r="K21" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L21" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M21" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="N21">
-        <v>2.9500000000000002</v>
+        <v>2.95</v>
       </c>
       <c r="O21" s="7"/>
       <c r="P21" s="7"/>
@@ -2400,45 +2454,45 @@
       <c r="Y21" s="7"/>
       <c r="Z21" s="7"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="F22" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D22" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="7" t="s">
+      <c r="G22" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="H22" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="G22" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I22" s="7" t="s">
+      <c r="J22" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="J22" s="8" t="s">
-        <v>118</v>
-      </c>
       <c r="K22" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L22" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M22" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="M22" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="N22">
         <v>3</v>
@@ -2456,48 +2510,48 @@
       <c r="Y22" s="7"/>
       <c r="Z22" s="7"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="F23" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="7" t="s">
+      <c r="G23" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="H23" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>123</v>
-      </c>
       <c r="J23" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L23" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M23" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M23" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="N23">
-        <v>3.0499999999999998</v>
+        <v>3.05</v>
       </c>
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
@@ -2512,48 +2566,48 @@
       <c r="Y23" s="7"/>
       <c r="Z23" s="7"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E24" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="F24" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E24" s="7" t="s">
+      <c r="G24" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="F24" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="H24" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I24" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="J24" s="8" t="s">
-        <v>122</v>
-      </c>
       <c r="K24" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L24" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M24" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="N24">
-        <v>3.1000000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="O24" s="7"/>
       <c r="P24" s="7"/>
@@ -2568,48 +2622,48 @@
       <c r="Y24" s="7"/>
       <c r="Z24" s="7"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" s="7" t="s">
+      <c r="G25" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="H25" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G25" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>131</v>
-      </c>
       <c r="J25" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L25" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M25" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M25" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="N25">
-        <v>3.1499999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="O25" s="7"/>
       <c r="P25" s="7"/>
@@ -2624,48 +2678,48 @@
       <c r="Y25" s="7"/>
       <c r="Z25" s="7"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
         <v>25</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>133</v>
-      </c>
       <c r="J26" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L26" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M26" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="N26">
-        <v>3.2000000000000002</v>
+        <v>3.2</v>
       </c>
       <c r="O26" s="7"/>
       <c r="P26" s="7"/>
@@ -2680,45 +2734,45 @@
       <c r="Y26" s="7"/>
       <c r="Z26" s="7"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27" s="7">
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="7" t="s">
+      <c r="G27" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="F27" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="H27" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I27" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="J27" s="8" t="s">
-        <v>116</v>
-      </c>
       <c r="K27" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L27" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M27" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="M27" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="N27">
         <v>3.25</v>
@@ -2736,45 +2790,45 @@
       <c r="Y27" s="7"/>
       <c r="Z27" s="7"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
         <v>27</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F28" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="7" t="s">
+      <c r="G28" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="F28" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="H28" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I28" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="J28" s="8" t="s">
-        <v>94</v>
-      </c>
       <c r="K28" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L28" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M28" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="M28" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="N28">
         <v>2</v>
@@ -2792,45 +2846,45 @@
       <c r="Y28" s="7"/>
       <c r="Z28" s="7"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29" s="7">
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" s="7" t="s">
+      <c r="G29" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="H29" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="G29" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I29" s="7" t="s">
+      <c r="J29" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="J29" s="8" t="s">
-        <v>144</v>
-      </c>
       <c r="K29" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L29" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M29" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="M29" s="11" t="s">
-        <v>25</v>
       </c>
       <c r="N29">
         <v>2.0499999999999998</v>
@@ -2848,48 +2902,48 @@
       <c r="Y29" s="7"/>
       <c r="Z29" s="7"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A30" s="7">
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F30" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" s="7" t="s">
+      <c r="G30" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="H30" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="G30" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>148</v>
-      </c>
       <c r="J30" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L30" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M30" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M30" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="N30">
-        <v>2.1000000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="O30" s="7"/>
       <c r="P30" s="7"/>
@@ -2904,48 +2958,48 @@
       <c r="Y30" s="7"/>
       <c r="Z30" s="7"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A31" s="7">
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F31" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" s="7" t="s">
+      <c r="G31" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="F31" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="H31" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I31" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="J31" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="J31" s="8" t="s">
-        <v>147</v>
-      </c>
       <c r="K31" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L31" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M31" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="N31">
-        <v>2.1499999999999999</v>
+        <v>2.15</v>
       </c>
       <c r="O31" s="7"/>
       <c r="P31" s="7"/>
@@ -2960,45 +3014,45 @@
       <c r="Y31" s="7"/>
       <c r="Z31" s="7"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M32" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K32" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L32" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M32" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="N32">
         <v>2.2000000000000002</v>
@@ -3016,45 +3070,45 @@
       <c r="Y32" s="7"/>
       <c r="Z32" s="7"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A33" s="7">
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M33" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K33" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L33" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M33" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="N33">
         <v>2.25</v>
@@ -3072,45 +3126,45 @@
       <c r="Y33" s="7"/>
       <c r="Z33" s="7"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D34" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M34" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="K34" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L34" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M34" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="N34">
         <v>2.2999999999999998</v>
@@ -3128,48 +3182,48 @@
       <c r="Y34" s="7"/>
       <c r="Z34" s="7"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A35" s="7">
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F35" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D35" s="12" t="s">
+      <c r="G35" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M35" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="K35" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L35" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M35" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="N35">
-        <v>2.3500000000000001</v>
+        <v>2.35</v>
       </c>
       <c r="O35" s="7"/>
       <c r="P35" s="7"/>
@@ -3184,48 +3238,48 @@
       <c r="Y35" s="7"/>
       <c r="Z35" s="7"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
         <v>35</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="K36" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M36" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E36" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="K36" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L36" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M36" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="N36">
-        <v>2.3999999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="O36" s="7"/>
       <c r="P36" s="7"/>
@@ -3240,45 +3294,45 @@
       <c r="Y36" s="7"/>
       <c r="Z36" s="7"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A37" s="7">
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D37" s="12" t="s">
+      <c r="G37" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K37" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M37" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="J37" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K37" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M37" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="N37">
         <v>2.4500000000000002</v>
@@ -3296,45 +3350,45 @@
       <c r="Y37" s="7"/>
       <c r="Z37" s="7"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
         <v>37</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C38" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F38" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="G38" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="K38" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M38" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I38" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="K38" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L38" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M38" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="N38">
         <v>2.5</v>
@@ -3352,45 +3406,45 @@
       <c r="Y38" s="7"/>
       <c r="Z38" s="7"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A39" s="7">
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="E39" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="C39" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D39" s="12" t="s">
+      <c r="F39" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="K39" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M39" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="J39" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="K39" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L39" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M39" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="N39">
         <v>2.5499999999999998</v>
@@ -3408,48 +3462,48 @@
       <c r="Y39" s="7"/>
       <c r="Z39" s="7"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A40" s="7">
         <v>39</v>
       </c>
       <c r="B40" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E40" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D40" s="12" t="s">
+      <c r="F40" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K40" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M40" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E40" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K40" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L40" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M40" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="N40">
-        <v>2.6000000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="O40" s="7"/>
       <c r="P40" s="7"/>
@@ -3464,48 +3518,48 @@
       <c r="Y40" s="7"/>
       <c r="Z40" s="7"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A41" s="7">
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E41" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="F41" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="G41" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="K41" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M41" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E41" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="K41" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L41" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M41" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="N41">
-        <v>2.6499999999999999</v>
+        <v>2.65</v>
       </c>
       <c r="O41" s="7"/>
       <c r="P41" s="7"/>
@@ -3520,48 +3574,48 @@
       <c r="Y41" s="7"/>
       <c r="Z41" s="7"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
         <v>41</v>
       </c>
       <c r="B42" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F42" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="G42" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="J42" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="K42" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M42" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E42" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="K42" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L42" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M42" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="N42">
-        <v>2.7000000000000002</v>
+        <v>2.7</v>
       </c>
       <c r="O42" s="7"/>
       <c r="P42" s="7"/>
@@ -3576,45 +3630,45 @@
       <c r="Y42" s="7"/>
       <c r="Z42" s="7"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A43" s="7">
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E43" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="F43" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="G43" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K43" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M43" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J43" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="K43" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L43" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M43" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="N43">
         <v>2.75</v>
@@ -3632,48 +3686,48 @@
       <c r="Y43" s="7"/>
       <c r="Z43" s="7"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A44" s="7">
         <v>43</v>
       </c>
       <c r="B44" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F44" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="C44" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D44" s="12" t="s">
+      <c r="G44" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="K44" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M44" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E44" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="K44" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L44" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M44" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="N44">
-        <v>2.7999999999999998</v>
+        <v>2.8</v>
       </c>
       <c r="O44" s="7"/>
       <c r="P44" s="7"/>
@@ -3688,48 +3742,48 @@
       <c r="Y44" s="7"/>
       <c r="Z44" s="7"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A45" s="7">
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F45" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="C45" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D45" s="12" t="s">
+      <c r="G45" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K45" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M45" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E45" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J45" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="K45" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L45" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M45" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="N45">
-        <v>2.8500000000000001</v>
+        <v>2.85</v>
       </c>
       <c r="O45" s="7"/>
       <c r="P45" s="7"/>
@@ -3744,48 +3798,48 @@
       <c r="Y45" s="7"/>
       <c r="Z45" s="7"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A46" s="7">
         <v>45</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D46" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="K46" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M46" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E46" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="K46" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L46" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M46" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="N46">
-        <v>2.8999999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="O46" s="7"/>
       <c r="P46" s="7"/>
@@ -3800,48 +3854,48 @@
       <c r="Y46" s="7"/>
       <c r="Z46" s="7"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A47" s="7">
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D47" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K47" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M47" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E47" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="J47" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="K47" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L47" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M47" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="N47">
-        <v>2.9500000000000002</v>
+        <v>2.95</v>
       </c>
       <c r="O47" s="7"/>
       <c r="P47" s="7"/>
@@ -3856,45 +3910,45 @@
       <c r="Y47" s="7"/>
       <c r="Z47" s="7"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A48" s="7">
         <v>47</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D48" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="K48" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M48" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I48" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="J48" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="K48" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L48" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M48" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="N48">
         <v>3</v>
@@ -3912,48 +3966,48 @@
       <c r="Y48" s="7"/>
       <c r="Z48" s="7"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A49" s="7">
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="D49" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="K49" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M49" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E49" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="J49" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="K49" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L49" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M49" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="N49">
-        <v>3.0499999999999998</v>
+        <v>3.05</v>
       </c>
       <c r="O49" s="7"/>
       <c r="P49" s="7"/>
@@ -3968,48 +4022,48 @@
       <c r="Y49" s="7"/>
       <c r="Z49" s="7"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A50" s="7">
         <v>49</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D50" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K50" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M50" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E50" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I50" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="J50" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K50" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L50" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M50" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="N50">
-        <v>3.1000000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="O50" s="7"/>
       <c r="P50" s="7"/>
@@ -4024,48 +4078,48 @@
       <c r="Y50" s="7"/>
       <c r="Z50" s="7"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A51" s="7">
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="E51" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="F51" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I51" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="J51" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="K51" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M51" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E51" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="J51" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="K51" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L51" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M51" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="N51">
-        <v>3.1499999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="O51" s="7"/>
       <c r="P51" s="7"/>
@@ -4080,48 +4134,48 @@
       <c r="Y51" s="7"/>
       <c r="Z51" s="7"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A52" s="7">
         <v>51</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D52" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="K52" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M52" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E52" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I52" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="J52" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="K52" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L52" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M52" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="N52">
-        <v>3.2000000000000002</v>
+        <v>3.2</v>
       </c>
       <c r="O52" s="7"/>
       <c r="P52" s="7"/>
@@ -4136,45 +4190,45 @@
       <c r="Y52" s="7"/>
       <c r="Z52" s="7"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A53" s="7">
         <v>52</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D53" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="K53" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M53" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I53" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="J53" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="K53" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L53" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M53" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="N53">
         <v>3.25</v>
@@ -4192,45 +4246,45 @@
       <c r="Y53" s="7"/>
       <c r="Z53" s="7"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A54" s="7">
         <v>53</v>
       </c>
       <c r="B54" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E54" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="D54" s="12" t="s">
+      <c r="F54" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="K54" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M54" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I54" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="J54" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="K54" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L54" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M54" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="N54">
         <v>2</v>
@@ -4248,45 +4302,45 @@
       <c r="Y54" s="7"/>
       <c r="Z54" s="7"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A55" s="7">
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E55" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="C55" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="D55" s="12" t="s">
+      <c r="F55" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="K55" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M55" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I55" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="J55" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="K55" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L55" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M55" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="N55">
         <v>2.0499999999999998</v>
@@ -4304,48 +4358,48 @@
       <c r="Y55" s="7"/>
       <c r="Z55" s="7"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A56" s="7">
         <v>55</v>
       </c>
       <c r="B56" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E56" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C56" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="D56" s="12" t="s">
+      <c r="F56" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="K56" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M56" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E56" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I56" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="J56" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="K56" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L56" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M56" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="N56">
-        <v>2.1000000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="O56" s="7"/>
       <c r="P56" s="7"/>
@@ -4360,48 +4414,48 @@
       <c r="Y56" s="7"/>
       <c r="Z56" s="7"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A57" s="7">
         <v>56</v>
       </c>
       <c r="B57" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="E57" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="F57" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="G57" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K57" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M57" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E57" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I57" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="J57" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="K57" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L57" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M57" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="N57">
-        <v>2.1499999999999999</v>
+        <v>2.15</v>
       </c>
       <c r="O57" s="7"/>
       <c r="P57" s="7"/>
@@ -4416,45 +4470,45 @@
       <c r="Y57" s="7"/>
       <c r="Z57" s="7"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A58" s="7">
         <v>57</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D58" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="K58" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M58" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I58" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="J58" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="K58" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L58" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M58" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="N58">
         <v>2.2000000000000002</v>
@@ -4472,45 +4526,45 @@
       <c r="Y58" s="7"/>
       <c r="Z58" s="7"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A59" s="7">
         <v>58</v>
       </c>
       <c r="B59" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="C59" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="D59" s="12" t="s">
+      <c r="J59" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="K59" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M59" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I59" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="J59" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="K59" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L59" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M59" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="N59">
         <v>2.25</v>
@@ -4528,45 +4582,45 @@
       <c r="Y59" s="7"/>
       <c r="Z59" s="7"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A60" s="7">
         <v>59</v>
       </c>
       <c r="B60" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I60" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C60" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D60" s="12" t="s">
+      <c r="J60" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K60" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M60" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H60" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I60" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="J60" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K60" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L60" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M60" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="N60">
         <v>2.2999999999999998</v>
@@ -4584,48 +4638,48 @@
       <c r="Y60" s="7"/>
       <c r="Z60" s="7"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A61" s="7">
         <v>60</v>
       </c>
       <c r="B61" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E61" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="C61" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="D61" s="12" t="s">
+      <c r="F61" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="K61" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M61" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E61" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G61" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I61" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="J61" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="K61" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L61" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M61" s="10" t="s">
-        <v>154</v>
-      </c>
       <c r="N61">
-        <v>2.3500000000000001</v>
+        <v>2.35</v>
       </c>
       <c r="O61" s="7"/>
       <c r="P61" s="7"/>
@@ -4640,26 +4694,26 @@
       <c r="Y61" s="7"/>
       <c r="Z61" s="7"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A62" s="7">
         <v>61</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="D62" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E62" s="7"/>
+      <c r="C62" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>201</v>
+      </c>
       <c r="F62" s="7"/>
-      <c r="G62" s="7" t="s">
+      <c r="G62" s="7"/>
+      <c r="H62" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H62" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I62" s="7"/>
       <c r="J62" s="7"/>
@@ -4667,7 +4721,7 @@
       <c r="L62" s="7"/>
       <c r="M62" s="7"/>
       <c r="N62">
-        <v>2.1499999999999999</v>
+        <v>2.15</v>
       </c>
       <c r="O62" s="7"/>
       <c r="P62" s="7"/>
@@ -4682,26 +4736,26 @@
       <c r="Y62" s="7"/>
       <c r="Z62" s="7"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A63" s="7">
         <v>62</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D63" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E63" s="7"/>
+      <c r="C63" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="F63" s="7"/>
-      <c r="G63" s="7" t="s">
+      <c r="G63" s="7"/>
+      <c r="H63" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I63" s="7"/>
       <c r="J63" s="7"/>
@@ -4724,26 +4778,26 @@
       <c r="Y63" s="7"/>
       <c r="Z63" s="7"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A64" s="7">
         <v>63</v>
       </c>
       <c r="B64" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="E64" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="C64" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="E64" s="7"/>
       <c r="F64" s="7"/>
-      <c r="G64" s="7" t="s">
+      <c r="G64" s="7"/>
+      <c r="H64" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H64" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I64" s="7"/>
       <c r="J64" s="7"/>
@@ -4766,26 +4820,26 @@
       <c r="Y64" s="7"/>
       <c r="Z64" s="7"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A65" s="7">
         <v>64</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="D65" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E65" s="7"/>
+      <c r="C65" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>164</v>
+      </c>
       <c r="F65" s="7"/>
-      <c r="G65" s="7" t="s">
+      <c r="G65" s="7"/>
+      <c r="H65" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H65" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I65" s="7"/>
       <c r="J65" s="7"/>
@@ -4808,26 +4862,26 @@
       <c r="Y65" s="7"/>
       <c r="Z65" s="7"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A66" s="7">
         <v>65</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D66" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E66" s="7"/>
+      <c r="C66" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>109</v>
+      </c>
       <c r="F66" s="7"/>
-      <c r="G66" s="7" t="s">
+      <c r="G66" s="7"/>
+      <c r="H66" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H66" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I66" s="7"/>
       <c r="J66" s="7"/>
@@ -4835,7 +4889,7 @@
       <c r="L66" s="7"/>
       <c r="M66" s="7"/>
       <c r="N66">
-        <v>2.3500000000000001</v>
+        <v>2.35</v>
       </c>
       <c r="O66" s="7"/>
       <c r="P66" s="7"/>
@@ -4850,26 +4904,26 @@
       <c r="Y66" s="7"/>
       <c r="Z66" s="7"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A67" s="7">
         <v>66</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D67" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E67" s="7"/>
+      <c r="C67" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="F67" s="7"/>
-      <c r="G67" s="7" t="s">
+      <c r="G67" s="7"/>
+      <c r="H67" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H67" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I67" s="7"/>
       <c r="J67" s="7"/>
@@ -4877,7 +4931,7 @@
       <c r="L67" s="7"/>
       <c r="M67" s="7"/>
       <c r="N67">
-        <v>2.3999999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="O67" s="7"/>
       <c r="P67" s="7"/>
@@ -4892,26 +4946,26 @@
       <c r="Y67" s="7"/>
       <c r="Z67" s="7"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A68" s="7">
         <v>67</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="D68" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E68" s="7"/>
+      <c r="C68" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="F68" s="7"/>
-      <c r="G68" s="7" t="s">
+      <c r="G68" s="7"/>
+      <c r="H68" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H68" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I68" s="7"/>
       <c r="J68" s="7"/>
@@ -4934,26 +4988,26 @@
       <c r="Y68" s="7"/>
       <c r="Z68" s="7"/>
     </row>
-    <row r="69">
-      <c r="A69" s="7">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A69" s="15">
         <v>68</v>
       </c>
-      <c r="B69" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D69" s="13" t="s">
+      <c r="B69" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="E69" s="7"/>
+      <c r="C69" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="E69" s="17" t="s">
+        <v>105</v>
+      </c>
       <c r="F69" s="7"/>
-      <c r="G69" s="7" t="s">
+      <c r="G69" s="7"/>
+      <c r="H69" s="15" t="s">
         <v>219</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I69" s="7"/>
       <c r="J69" s="7"/>
@@ -4976,26 +5030,26 @@
       <c r="Y69" s="7"/>
       <c r="Z69" s="7"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A70" s="7">
         <v>69</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D70" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E70" s="7"/>
+      <c r="C70" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>164</v>
+      </c>
       <c r="F70" s="7"/>
-      <c r="G70" s="7" t="s">
+      <c r="G70" s="7"/>
+      <c r="H70" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H70" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I70" s="7"/>
       <c r="J70" s="7"/>
@@ -5018,26 +5072,26 @@
       <c r="Y70" s="7"/>
       <c r="Z70" s="7"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A71" s="7">
         <v>70</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D71" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E71" s="7"/>
+      <c r="C71" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="F71" s="7"/>
-      <c r="G71" s="7" t="s">
+      <c r="G71" s="7"/>
+      <c r="H71" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I71" s="7"/>
       <c r="J71" s="7"/>
@@ -5045,7 +5099,7 @@
       <c r="L71" s="7"/>
       <c r="M71" s="7"/>
       <c r="N71">
-        <v>2.6000000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="O71" s="7"/>
       <c r="P71" s="7"/>
@@ -5060,26 +5114,26 @@
       <c r="Y71" s="7"/>
       <c r="Z71" s="7"/>
     </row>
-    <row r="72">
-      <c r="A72" s="7">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A72" s="14">
         <v>71</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="D72" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E72" s="7"/>
+      <c r="C72" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="F72" s="7"/>
-      <c r="G72" s="7" t="s">
+      <c r="G72" s="7"/>
+      <c r="H72" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H72" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I72" s="7"/>
       <c r="J72" s="7"/>
@@ -5087,7 +5141,7 @@
       <c r="L72" s="7"/>
       <c r="M72" s="7"/>
       <c r="N72">
-        <v>2.6499999999999999</v>
+        <v>2.65</v>
       </c>
       <c r="O72" s="7"/>
       <c r="P72" s="7"/>
@@ -5102,26 +5156,26 @@
       <c r="Y72" s="7"/>
       <c r="Z72" s="7"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A73" s="7">
         <v>72</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D73" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E73" s="7"/>
+      <c r="C73" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="F73" s="7"/>
-      <c r="G73" s="7" t="s">
+      <c r="G73" s="7"/>
+      <c r="H73" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H73" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I73" s="7"/>
       <c r="J73" s="7"/>
@@ -5129,7 +5183,7 @@
       <c r="L73" s="7"/>
       <c r="M73" s="7"/>
       <c r="N73">
-        <v>2.7000000000000002</v>
+        <v>2.7</v>
       </c>
       <c r="O73" s="7"/>
       <c r="P73" s="7"/>
@@ -5144,26 +5198,26 @@
       <c r="Y73" s="7"/>
       <c r="Z73" s="7"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A74" s="7">
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="D74" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E74" s="7"/>
+      <c r="C74" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="F74" s="7"/>
-      <c r="G74" s="7" t="s">
+      <c r="G74" s="7"/>
+      <c r="H74" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H74" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I74" s="7"/>
       <c r="J74" s="7"/>
@@ -5186,26 +5240,26 @@
       <c r="Y74" s="7"/>
       <c r="Z74" s="7"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A75" s="7">
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="D75" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E75" s="7"/>
+      <c r="C75" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>222</v>
+      </c>
       <c r="F75" s="7"/>
-      <c r="G75" s="7" t="s">
+      <c r="G75" s="7"/>
+      <c r="H75" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H75" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I75" s="7"/>
       <c r="J75" s="7"/>
@@ -5213,7 +5267,7 @@
       <c r="L75" s="7"/>
       <c r="M75" s="7"/>
       <c r="N75">
-        <v>2.7999999999999998</v>
+        <v>2.8</v>
       </c>
       <c r="O75" s="7"/>
       <c r="P75" s="7"/>
@@ -5228,26 +5282,26 @@
       <c r="Y75" s="7"/>
       <c r="Z75" s="7"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A76" s="7">
         <v>75</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D76" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E76" s="7"/>
+      <c r="C76" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>262</v>
+      </c>
       <c r="F76" s="7"/>
-      <c r="G76" s="7" t="s">
+      <c r="G76" s="7"/>
+      <c r="H76" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H76" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I76" s="7"/>
       <c r="J76" s="7"/>
@@ -5255,7 +5309,7 @@
       <c r="L76" s="7"/>
       <c r="M76" s="7"/>
       <c r="N76">
-        <v>2.8500000000000001</v>
+        <v>2.85</v>
       </c>
       <c r="O76" s="7"/>
       <c r="P76" s="7"/>
@@ -5270,26 +5324,26 @@
       <c r="Y76" s="7"/>
       <c r="Z76" s="7"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A77" s="7">
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D77" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E77" s="7"/>
+      <c r="C77" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>96</v>
+      </c>
       <c r="F77" s="7"/>
-      <c r="G77" s="7" t="s">
+      <c r="G77" s="7"/>
+      <c r="H77" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H77" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I77" s="7"/>
       <c r="J77" s="7"/>
@@ -5297,7 +5351,7 @@
       <c r="L77" s="7"/>
       <c r="M77" s="7"/>
       <c r="N77">
-        <v>2.8999999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="O77" s="7"/>
       <c r="P77" s="7"/>
@@ -5312,26 +5366,26 @@
       <c r="Y77" s="7"/>
       <c r="Z77" s="7"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A78" s="7">
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="D78" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E78" s="7"/>
+      <c r="C78" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>233</v>
+      </c>
       <c r="F78" s="7"/>
-      <c r="G78" s="7" t="s">
+      <c r="G78" s="7"/>
+      <c r="H78" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H78" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I78" s="7"/>
       <c r="J78" s="7"/>
@@ -5339,7 +5393,7 @@
       <c r="L78" s="7"/>
       <c r="M78" s="7"/>
       <c r="N78">
-        <v>2.9500000000000002</v>
+        <v>2.95</v>
       </c>
       <c r="O78" s="7"/>
       <c r="P78" s="7"/>
@@ -5354,26 +5408,26 @@
       <c r="Y78" s="7"/>
       <c r="Z78" s="7"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A79" s="7">
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="D79" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E79" s="7"/>
+      <c r="C79" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>235</v>
+      </c>
       <c r="F79" s="7"/>
-      <c r="G79" s="7" t="s">
+      <c r="G79" s="7"/>
+      <c r="H79" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H79" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I79" s="7"/>
       <c r="J79" s="7"/>
@@ -5396,26 +5450,26 @@
       <c r="Y79" s="7"/>
       <c r="Z79" s="7"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A80" s="7">
         <v>79</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="D80" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E80" s="7"/>
+      <c r="C80" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>237</v>
+      </c>
       <c r="F80" s="7"/>
-      <c r="G80" s="7" t="s">
+      <c r="G80" s="7"/>
+      <c r="H80" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H80" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I80" s="7"/>
       <c r="J80" s="7"/>
@@ -5423,7 +5477,7 @@
       <c r="L80" s="7"/>
       <c r="M80" s="7"/>
       <c r="N80">
-        <v>3.0499999999999998</v>
+        <v>3.05</v>
       </c>
       <c r="O80" s="7"/>
       <c r="P80" s="7"/>
@@ -5438,26 +5492,26 @@
       <c r="Y80" s="7"/>
       <c r="Z80" s="7"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A81" s="7">
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D81" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E81" s="7"/>
+      <c r="C81" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="F81" s="7"/>
-      <c r="G81" s="7" t="s">
+      <c r="G81" s="7"/>
+      <c r="H81" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H81" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I81" s="7"/>
       <c r="J81" s="7"/>
@@ -5465,7 +5519,7 @@
       <c r="L81" s="7"/>
       <c r="M81" s="7"/>
       <c r="N81">
-        <v>3.1000000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="O81" s="7"/>
       <c r="P81" s="7"/>
@@ -5480,26 +5534,26 @@
       <c r="Y81" s="7"/>
       <c r="Z81" s="7"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A82" s="7">
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="D82" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E82" s="7"/>
+      <c r="C82" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>240</v>
+      </c>
       <c r="F82" s="7"/>
-      <c r="G82" s="7" t="s">
+      <c r="G82" s="7"/>
+      <c r="H82" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H82" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I82" s="7"/>
       <c r="J82" s="7"/>
@@ -5507,7 +5561,7 @@
       <c r="L82" s="7"/>
       <c r="M82" s="7"/>
       <c r="N82">
-        <v>3.1499999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="O82" s="7"/>
       <c r="P82" s="7"/>
@@ -5522,26 +5576,26 @@
       <c r="Y82" s="7"/>
       <c r="Z82" s="7"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A83" s="7">
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D83" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E83" s="7"/>
+      <c r="C83" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>26</v>
+      </c>
       <c r="F83" s="7"/>
-      <c r="G83" s="7" t="s">
+      <c r="G83" s="7"/>
+      <c r="H83" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H83" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I83" s="7"/>
       <c r="J83" s="7"/>
@@ -5549,7 +5603,7 @@
       <c r="L83" s="7"/>
       <c r="M83" s="7"/>
       <c r="N83">
-        <v>3.2000000000000002</v>
+        <v>3.2</v>
       </c>
       <c r="O83" s="7"/>
       <c r="P83" s="7"/>
@@ -5564,26 +5618,26 @@
       <c r="Y83" s="7"/>
       <c r="Z83" s="7"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A84" s="7">
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="D84" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E84" s="7"/>
+      <c r="C84" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>243</v>
+      </c>
       <c r="F84" s="7"/>
-      <c r="G84" s="7" t="s">
+      <c r="G84" s="7"/>
+      <c r="H84" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H84" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I84" s="7"/>
       <c r="J84" s="7"/>
@@ -5606,26 +5660,26 @@
       <c r="Y84" s="7"/>
       <c r="Z84" s="7"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A85" s="7">
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="D85" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E85" s="7"/>
+      <c r="C85" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>215</v>
+      </c>
       <c r="F85" s="7"/>
-      <c r="G85" s="7" t="s">
+      <c r="G85" s="7"/>
+      <c r="H85" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H85" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I85" s="7"/>
       <c r="J85" s="7"/>
@@ -5648,26 +5702,26 @@
       <c r="Y85" s="7"/>
       <c r="Z85" s="7"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A86" s="7">
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="D86" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E86" s="7"/>
+      <c r="C86" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>124</v>
+      </c>
       <c r="F86" s="7"/>
-      <c r="G86" s="7" t="s">
+      <c r="G86" s="7"/>
+      <c r="H86" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H86" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I86" s="7"/>
       <c r="J86" s="7"/>
@@ -5690,26 +5744,26 @@
       <c r="Y86" s="7"/>
       <c r="Z86" s="7"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A87" s="7">
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="D87" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E87" s="7"/>
+      <c r="C87" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>247</v>
+      </c>
       <c r="F87" s="7"/>
-      <c r="G87" s="7" t="s">
+      <c r="G87" s="7"/>
+      <c r="H87" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H87" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I87" s="7"/>
       <c r="J87" s="7"/>
@@ -5717,7 +5771,7 @@
       <c r="L87" s="7"/>
       <c r="M87" s="7"/>
       <c r="N87">
-        <v>2.1000000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="O87" s="7"/>
       <c r="P87" s="7"/>
@@ -5732,26 +5786,26 @@
       <c r="Y87" s="7"/>
       <c r="Z87" s="7"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A88" s="7">
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D88" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E88" s="7"/>
+      <c r="C88" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="F88" s="7"/>
-      <c r="G88" s="7" t="s">
+      <c r="G88" s="7"/>
+      <c r="H88" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H88" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I88" s="7"/>
       <c r="J88" s="7"/>
@@ -5759,7 +5813,7 @@
       <c r="L88" s="7"/>
       <c r="M88" s="7"/>
       <c r="N88">
-        <v>2.1499999999999999</v>
+        <v>2.15</v>
       </c>
       <c r="O88" s="7"/>
       <c r="P88" s="7"/>
@@ -5774,26 +5828,26 @@
       <c r="Y88" s="7"/>
       <c r="Z88" s="7"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A89" s="7">
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="D89" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E89" s="7"/>
+      <c r="C89" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>250</v>
+      </c>
       <c r="F89" s="7"/>
-      <c r="G89" s="7" t="s">
+      <c r="G89" s="7"/>
+      <c r="H89" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I89" s="7"/>
       <c r="J89" s="7"/>
@@ -5816,26 +5870,26 @@
       <c r="Y89" s="7"/>
       <c r="Z89" s="7"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A90" s="7">
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D90" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E90" s="7"/>
+      <c r="C90" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>26</v>
+      </c>
       <c r="F90" s="7"/>
-      <c r="G90" s="7" t="s">
+      <c r="G90" s="7"/>
+      <c r="H90" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H90" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I90" s="7"/>
       <c r="J90" s="7"/>
@@ -5858,26 +5912,26 @@
       <c r="Y90" s="7"/>
       <c r="Z90" s="7"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A91" s="7">
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="D91" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E91" s="7"/>
+      <c r="C91" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>253</v>
+      </c>
       <c r="F91" s="7"/>
-      <c r="G91" s="7" t="s">
+      <c r="G91" s="7"/>
+      <c r="H91" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="I91" s="7"/>
       <c r="J91" s="7"/>
@@ -5901,8 +5955,9 @@
       <c r="Z91" s="7"/>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C2" numberStoredAsText="1"/>
+    <ignoredError sqref="E2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>